--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,6780 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127981516</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>519856</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6524816</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127988398</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>519897</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6524632</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127979097</v>
+      </c>
+      <c r="B5" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520012</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6524809</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127948538</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79641</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520098</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6524835</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127986450</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92659</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>519639</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6524788</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127983115</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>519891</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6524716</v>
+      </c>
+      <c r="S8" t="n">
+        <v>150</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127986585</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>519663</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6524783</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127980622</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>519968</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6524851</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127984949</v>
+      </c>
+      <c r="B11" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>519552</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6524907</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127949128</v>
+      </c>
+      <c r="B12" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>520070</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6524851</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127981103</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>519953</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6524860</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127988511</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>519885</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6524640</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127948647</v>
+      </c>
+      <c r="B15" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>520100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6524842</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127979875</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96061</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>519924</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6524793</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127985911</v>
+      </c>
+      <c r="B17" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>519623</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6524788</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127978774</v>
+      </c>
+      <c r="B18" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>520015</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6524853</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127985273</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>519561</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6524849</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127983089</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>519891</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6524716</v>
+      </c>
+      <c r="S20" t="n">
+        <v>150</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127982168</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>519819</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6524878</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127982418</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>519808</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6524877</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127985397</v>
+      </c>
+      <c r="B23" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>519560</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6524839</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127948923</v>
+      </c>
+      <c r="B24" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>520075</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6524840</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127950402</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>520020</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6524923</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127950272</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>520031</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6524880</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127949748</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>520046</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6524882</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127982588</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>519798</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6524851</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127984194</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>519680</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6524874</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127988256</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96061</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>519889</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6524614</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127948850</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>520085</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6524846</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127984020</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>519675</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6524829</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127948430</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>520103</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6524835</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127987178</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>519677</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6524696</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127948726</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>520092</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6524842</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127987059</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>519688</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6524694</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127950052</v>
+      </c>
+      <c r="B37" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>520044</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6524903</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127986395</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92623</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>519639</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6524788</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127986860</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>519744</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6524735</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127978914</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92631</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>520021</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6524832</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127988102</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>519876</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6524610</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127979704</v>
+      </c>
+      <c r="B42" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>519952</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6524773</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127982266</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>519814</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6524877</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127980473</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>519985</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6524831</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127981664</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>519843</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6524831</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127983788</v>
+      </c>
+      <c r="B46" t="n">
+        <v>96061</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>519717</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6524808</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127985707</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>519596</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6524811</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127980279</v>
+      </c>
+      <c r="B48" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>519975</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6524804</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127984700</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80998</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>519633</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6524919</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127983540</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>519733</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6524792</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127949218</v>
+      </c>
+      <c r="B51" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>520067</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6524857</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127987902</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>519738</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6524605</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127979471</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>519986</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6524777</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127950593</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>519991</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6524893</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127949357</v>
+      </c>
+      <c r="B55" t="n">
+        <v>40076</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>520055</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6524858</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127981257</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79109</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>519957</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6524845</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127984457</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6272</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>519670</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6524879</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127984642</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>519633</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6524919</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127979259</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>520006</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6524801</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127980871</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79023</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>519964</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6524859</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>på tall</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127985560</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>519553</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6524821</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127980055</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>519943</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6524799</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127985115</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>519590</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6524878</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127989334</v>
+      </c>
+      <c r="B64" t="n">
+        <v>96061</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>519962</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6524616</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127983362</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>519743</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6524836</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,43 +788,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127981516</v>
+        <v>127948538</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519856</v>
+        <v>520098</v>
       </c>
       <c r="R3" t="n">
-        <v>6524816</v>
+        <v>6524835</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127988398</v>
+        <v>127986585</v>
       </c>
       <c r="B4" t="n">
         <v>8450</v>
@@ -939,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519897</v>
+        <v>519663</v>
       </c>
       <c r="R4" t="n">
-        <v>6524632</v>
+        <v>6524783</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1113,41 +1110,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127948538</v>
+        <v>127988398</v>
       </c>
       <c r="B6" t="n">
-        <v>79641</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520098</v>
+        <v>519897</v>
       </c>
       <c r="R6" t="n">
-        <v>6524835</v>
+        <v>6524632</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1199,6 +1198,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,41 +1217,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127986450</v>
+        <v>127981516</v>
       </c>
       <c r="B7" t="n">
-        <v>92659</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519639</v>
+        <v>519856</v>
       </c>
       <c r="R7" t="n">
-        <v>6524788</v>
+        <v>6524816</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127983115</v>
+        <v>127986450</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>92659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,35 +1335,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,13 +1366,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519891</v>
+        <v>519639</v>
       </c>
       <c r="R8" t="n">
-        <v>6524716</v>
+        <v>6524788</v>
       </c>
       <c r="S8" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,6 +1410,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1431,41 +1429,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127986585</v>
+        <v>127983115</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1475,13 +1476,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519663</v>
+        <v>519891</v>
       </c>
       <c r="R9" t="n">
-        <v>6524783</v>
+        <v>6524716</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1520,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127949128</v>
+        <v>127981103</v>
       </c>
       <c r="B12" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520070</v>
+        <v>519953</v>
       </c>
       <c r="R12" t="n">
-        <v>6524851</v>
+        <v>6524860</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,11 +1836,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127981103</v>
+        <v>127988511</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1911,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519953</v>
+        <v>519885</v>
       </c>
       <c r="R13" t="n">
-        <v>6524860</v>
+        <v>6524640</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1955,6 +1950,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127988511</v>
+        <v>127948647</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519885</v>
+        <v>520100</v>
       </c>
       <c r="R14" t="n">
-        <v>6524640</v>
+        <v>6524842</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2055,13 +2051,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127948647</v>
+        <v>127949128</v>
       </c>
       <c r="B15" t="n">
         <v>40076</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520100</v>
+        <v>520070</v>
       </c>
       <c r="R15" t="n">
-        <v>6524842</v>
+        <v>6524851</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2626,44 +2626,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127983089</v>
+        <v>127982168</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2673,13 +2670,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519891</v>
+        <v>519819</v>
       </c>
       <c r="R20" t="n">
-        <v>6524716</v>
+        <v>6524878</v>
       </c>
       <c r="S20" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2717,6 +2714,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2735,7 +2733,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982168</v>
+        <v>127982418</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2779,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519819</v>
+        <v>519808</v>
       </c>
       <c r="R21" t="n">
-        <v>6524878</v>
+        <v>6524877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2842,41 +2840,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127982418</v>
+        <v>127983089</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2886,13 +2887,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519808</v>
+        <v>519891</v>
       </c>
       <c r="R22" t="n">
-        <v>6524877</v>
+        <v>6524716</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2931,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127950402</v>
+        <v>127949748</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520020</v>
+        <v>520046</v>
       </c>
       <c r="R25" t="n">
-        <v>6524923</v>
+        <v>6524882</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127950272</v>
+        <v>127982588</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520031</v>
+        <v>519798</v>
       </c>
       <c r="R26" t="n">
-        <v>6524880</v>
+        <v>6524851</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3366,6 +3366,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3384,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127949748</v>
+        <v>127950272</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3428,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520046</v>
+        <v>520031</v>
       </c>
       <c r="R27" t="n">
-        <v>6524882</v>
+        <v>6524880</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3490,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127982588</v>
+        <v>127950402</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3534,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519798</v>
+        <v>520020</v>
       </c>
       <c r="R28" t="n">
-        <v>6524851</v>
+        <v>6524923</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3578,7 +3579,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R31" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,6 +3898,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3916,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3960,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R32" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4004,7 +4005,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127948430</v>
+        <v>127948726</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +4034,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520103</v>
+        <v>520092</v>
       </c>
       <c r="R33" t="n">
-        <v>6524835</v>
+        <v>6524842</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127987178</v>
+        <v>127948430</v>
       </c>
       <c r="B34" t="n">
         <v>8450</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519677</v>
+        <v>520103</v>
       </c>
       <c r="R34" t="n">
-        <v>6524696</v>
+        <v>6524835</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4217,7 +4217,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4236,10 +4235,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127948726</v>
+        <v>127987178</v>
       </c>
       <c r="B35" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,21 +4246,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4280,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520092</v>
+        <v>519677</v>
       </c>
       <c r="R35" t="n">
-        <v>6524842</v>
+        <v>6524696</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4324,6 +4323,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4342,43 +4342,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127987059</v>
+        <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>92623</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519688</v>
+        <v>519639</v>
       </c>
       <c r="R36" t="n">
-        <v>6524694</v>
+        <v>6524788</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4560,41 +4558,43 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127986395</v>
+        <v>127987059</v>
       </c>
       <c r="B38" t="n">
-        <v>92623</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519639</v>
+        <v>519688</v>
       </c>
       <c r="R38" t="n">
-        <v>6524788</v>
+        <v>6524694</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127986860</v>
+        <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,32 +4676,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4709,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519744</v>
+        <v>520021</v>
       </c>
       <c r="R39" t="n">
-        <v>6524735</v>
+        <v>6524832</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4753,7 +4751,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4772,10 +4769,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127978914</v>
+        <v>127988102</v>
       </c>
       <c r="B40" t="n">
-        <v>92631</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4783,30 +4780,32 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4814,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520021</v>
+        <v>519876</v>
       </c>
       <c r="R40" t="n">
-        <v>6524832</v>
+        <v>6524610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4858,6 +4857,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B41" t="n">
         <v>8450</v>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R41" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127979704</v>
+        <v>127982266</v>
       </c>
       <c r="B42" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519952</v>
+        <v>519814</v>
       </c>
       <c r="R42" t="n">
-        <v>6524773</v>
+        <v>6524877</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5065,17 +5065,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5094,7 +5090,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127982266</v>
+        <v>127980473</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5138,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519814</v>
+        <v>519985</v>
       </c>
       <c r="R43" t="n">
-        <v>6524877</v>
+        <v>6524831</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5182,7 +5178,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5201,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127980473</v>
+        <v>127983788</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>96061</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,32 +5207,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5245,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519985</v>
+        <v>519717</v>
       </c>
       <c r="R44" t="n">
-        <v>6524831</v>
+        <v>6524808</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5289,6 +5283,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5409,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B46" t="n">
-        <v>96061</v>
+        <v>40076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5425,31 +5420,32 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5457,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R46" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5495,13 +5491,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,21 +5531,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R47" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5602,13 +5602,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5627,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B48" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5642,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5671,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R48" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5690,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5696,7 +5700,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5709,17 +5713,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127983540</v>
+        <v>127949357</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519733</v>
+        <v>520055</v>
       </c>
       <c r="R50" t="n">
-        <v>6524792</v>
+        <v>6524858</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5925,13 +5925,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5950,10 +5954,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127949218</v>
+        <v>127950593</v>
       </c>
       <c r="B51" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5961,21 +5965,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5998,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520067</v>
+        <v>519991</v>
       </c>
       <c r="R51" t="n">
-        <v>6524857</v>
+        <v>6524893</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6030,11 +6034,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6061,10 +6060,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127987902</v>
+        <v>127979471</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6072,21 +6071,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6105,10 +6104,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519738</v>
+        <v>519986</v>
       </c>
       <c r="R52" t="n">
-        <v>6524605</v>
+        <v>6524777</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6149,7 +6148,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6168,10 +6166,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127979471</v>
+        <v>127949218</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>40076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6179,21 +6177,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6212,10 +6210,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519986</v>
+        <v>520067</v>
       </c>
       <c r="R53" t="n">
-        <v>6524777</v>
+        <v>6524857</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6248,6 +6246,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6274,10 +6277,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127950593</v>
+        <v>127987902</v>
       </c>
       <c r="B54" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6285,21 +6288,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6318,10 +6321,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519991</v>
+        <v>519738</v>
       </c>
       <c r="R54" t="n">
-        <v>6524893</v>
+        <v>6524605</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6362,6 +6365,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6380,10 +6384,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127949357</v>
+        <v>127983540</v>
       </c>
       <c r="B55" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,21 +6395,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6428,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520055</v>
+        <v>519733</v>
       </c>
       <c r="R55" t="n">
-        <v>6524858</v>
+        <v>6524792</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6462,17 +6466,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127981257</v>
+        <v>127984457</v>
       </c>
       <c r="B56" t="n">
-        <v>79109</v>
+        <v>6272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,30 +6502,32 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6450</v>
+        <v>105336</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6533,10 +6535,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519957</v>
+        <v>519670</v>
       </c>
       <c r="R56" t="n">
-        <v>6524845</v>
+        <v>6524879</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6596,10 +6598,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127984457</v>
+        <v>127979259</v>
       </c>
       <c r="B57" t="n">
-        <v>6272</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,32 +6609,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6640,10 +6642,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519670</v>
+        <v>520006</v>
       </c>
       <c r="R57" t="n">
-        <v>6524879</v>
+        <v>6524801</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6684,7 +6686,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6810,10 +6811,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127979259</v>
+        <v>127981257</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6821,32 +6822,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6450</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6854,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520006</v>
+        <v>519957</v>
       </c>
       <c r="R59" t="n">
-        <v>6524801</v>
+        <v>6524845</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6898,6 +6897,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6916,45 +6916,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127980871</v>
+        <v>127985560</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6962,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519964</v>
+        <v>519553</v>
       </c>
       <c r="R60" t="n">
-        <v>6524859</v>
+        <v>6524821</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6977,7 +6975,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6987,7 +6985,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -7000,17 +6998,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>på tall</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7029,43 +7023,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985560</v>
+        <v>127980871</v>
       </c>
       <c r="B61" t="n">
-        <v>8439</v>
+        <v>79023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7073,10 +7069,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519553</v>
+        <v>519964</v>
       </c>
       <c r="R61" t="n">
-        <v>6524821</v>
+        <v>6524859</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7088,7 +7084,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -7098,7 +7094,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -7111,13 +7107,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>på tall</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127980055</v>
+        <v>127985115</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519943</v>
+        <v>519590</v>
       </c>
       <c r="R62" t="n">
-        <v>6524799</v>
+        <v>6524878</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7224,6 +7224,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7242,7 +7243,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127985115</v>
+        <v>127980055</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -7286,10 +7287,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519590</v>
+        <v>519943</v>
       </c>
       <c r="R63" t="n">
-        <v>6524878</v>
+        <v>6524799</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7301,7 +7302,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -7311,7 +7312,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -7330,7 +7331,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B64" t="n">
-        <v>96061</v>
+        <v>8439</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,31 +7360,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7392,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R64" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7455,10 +7456,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B65" t="n">
-        <v>8439</v>
+        <v>96061</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7466,32 +7467,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R65" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>127948538</v>
       </c>
       <c r="B3" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127986585</v>
+        <v>127979097</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519663</v>
+        <v>520012</v>
       </c>
       <c r="R4" t="n">
-        <v>6524783</v>
+        <v>6524809</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,13 +974,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127979097</v>
+        <v>127986585</v>
       </c>
       <c r="B5" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520012</v>
+        <v>519663</v>
       </c>
       <c r="R5" t="n">
-        <v>6524809</v>
+        <v>6524783</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,17 +1085,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1324,41 +1324,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127986450</v>
+        <v>127980622</v>
       </c>
       <c r="B8" t="n">
-        <v>92659</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1366,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519639</v>
+        <v>519968</v>
       </c>
       <c r="R8" t="n">
-        <v>6524788</v>
+        <v>6524851</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,7 +1412,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127983115</v>
+        <v>127986450</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>92667</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,35 +1441,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,13 +1472,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519891</v>
+        <v>519639</v>
       </c>
       <c r="R9" t="n">
-        <v>6524716</v>
+        <v>6524788</v>
       </c>
       <c r="S9" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,6 +1516,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1538,41 +1535,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127980622</v>
+        <v>127983115</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519968</v>
+        <v>519891</v>
       </c>
       <c r="R10" t="n">
-        <v>6524851</v>
+        <v>6524716</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127981103</v>
+        <v>127948647</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519953</v>
+        <v>520100</v>
       </c>
       <c r="R12" t="n">
-        <v>6524860</v>
+        <v>6524842</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,6 +1836,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127988511</v>
+        <v>127949128</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519885</v>
+        <v>520070</v>
       </c>
       <c r="R13" t="n">
-        <v>6524640</v>
+        <v>6524851</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1944,13 +1949,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127948647</v>
+        <v>127981103</v>
       </c>
       <c r="B14" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1989,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520100</v>
+        <v>519953</v>
       </c>
       <c r="R14" t="n">
-        <v>6524842</v>
+        <v>6524860</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2049,11 +2058,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127949128</v>
+        <v>127988511</v>
       </c>
       <c r="B15" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520070</v>
+        <v>519885</v>
       </c>
       <c r="R15" t="n">
-        <v>6524851</v>
+        <v>6524640</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2162,17 +2166,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>127979875</v>
       </c>
       <c r="B16" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>127983089</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127949748</v>
+        <v>127982588</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520046</v>
+        <v>519798</v>
       </c>
       <c r="R25" t="n">
-        <v>6524882</v>
+        <v>6524851</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,6 +3260,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3278,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127982588</v>
+        <v>127950272</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3322,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519798</v>
+        <v>520031</v>
       </c>
       <c r="R26" t="n">
-        <v>6524851</v>
+        <v>6524880</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3366,7 +3367,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950272</v>
+        <v>127950402</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520031</v>
+        <v>520020</v>
       </c>
       <c r="R27" t="n">
-        <v>6524880</v>
+        <v>6524923</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127950402</v>
+        <v>127949748</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520020</v>
+        <v>520046</v>
       </c>
       <c r="R28" t="n">
-        <v>6524923</v>
+        <v>6524882</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3707,7 +3707,7 @@
         <v>127988256</v>
       </c>
       <c r="B30" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127982266</v>
+        <v>127983788</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>96069</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,32 +4994,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519814</v>
+        <v>519717</v>
       </c>
       <c r="R42" t="n">
-        <v>6524877</v>
+        <v>6524808</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5090,10 +5089,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127980473</v>
+        <v>127981664</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>4773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,21 +5100,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,7 +5133,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519985</v>
+        <v>519843</v>
       </c>
       <c r="R43" t="n">
         <v>6524831</v>
@@ -5178,6 +5177,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5196,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B44" t="n">
-        <v>96061</v>
+        <v>40076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,31 +5207,32 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5239,10 +5240,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R44" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5277,13 +5278,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5302,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127981664</v>
+        <v>127982266</v>
       </c>
       <c r="B45" t="n">
-        <v>4773</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5313,21 +5318,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5351,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519843</v>
+        <v>519814</v>
       </c>
       <c r="R45" t="n">
-        <v>6524831</v>
+        <v>6524877</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5409,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127979704</v>
+        <v>127980473</v>
       </c>
       <c r="B46" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5420,21 +5425,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5453,10 +5458,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519952</v>
+        <v>519985</v>
       </c>
       <c r="R46" t="n">
-        <v>6524773</v>
+        <v>6524831</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5489,11 +5494,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,43 +5520,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127980279</v>
+        <v>127984700</v>
       </c>
       <c r="B47" t="n">
-        <v>40076</v>
+        <v>81004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>214803</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5564,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519975</v>
+        <v>519633</v>
       </c>
       <c r="R47" t="n">
-        <v>6524804</v>
+        <v>6524919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5602,17 +5600,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5625,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,21 +5636,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R48" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5690,7 +5684,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5700,7 +5694,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5713,13 +5707,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,41 +5736,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127984700</v>
+        <v>127985707</v>
       </c>
       <c r="B49" t="n">
-        <v>80998</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519633</v>
+        <v>519596</v>
       </c>
       <c r="R49" t="n">
-        <v>6524919</v>
+        <v>6524811</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5954,10 +5954,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127950593</v>
+        <v>127949218</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>40076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,21 +5965,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519991</v>
+        <v>520067</v>
       </c>
       <c r="R51" t="n">
-        <v>6524893</v>
+        <v>6524857</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6034,6 +6034,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6060,7 +6065,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127979471</v>
+        <v>127950593</v>
       </c>
       <c r="B52" t="n">
         <v>8439</v>
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519986</v>
+        <v>519991</v>
       </c>
       <c r="R52" t="n">
-        <v>6524777</v>
+        <v>6524893</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6166,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127949218</v>
+        <v>127979471</v>
       </c>
       <c r="B53" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6177,21 +6182,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520067</v>
+        <v>519986</v>
       </c>
       <c r="R53" t="n">
-        <v>6524857</v>
+        <v>6524777</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6246,11 +6251,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6814,7 +6814,7 @@
         <v>127981257</v>
       </c>
       <c r="B59" t="n">
-        <v>79109</v>
+        <v>79115</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6916,43 +6916,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127985560</v>
+        <v>127980871</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6960,10 +6962,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519553</v>
+        <v>519964</v>
       </c>
       <c r="R60" t="n">
-        <v>6524821</v>
+        <v>6524859</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6975,7 +6977,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6985,7 +6987,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -6998,13 +7000,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>på tall</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7023,45 +7029,43 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127980871</v>
+        <v>127985560</v>
       </c>
       <c r="B61" t="n">
-        <v>79023</v>
+        <v>8439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7069,10 +7073,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519964</v>
+        <v>519553</v>
       </c>
       <c r="R61" t="n">
-        <v>6524859</v>
+        <v>6524821</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7084,7 +7088,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -7094,7 +7098,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -7107,17 +7111,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>på tall</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>8439</v>
+        <v>96069</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,32 +7360,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7393,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R64" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7456,10 +7455,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B65" t="n">
-        <v>96061</v>
+        <v>8439</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,31 +7466,32 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R65" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127948538</v>
+        <v>127986450</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>92668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,27 +799,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520098</v>
+        <v>519639</v>
       </c>
       <c r="R3" t="n">
-        <v>6524835</v>
+        <v>6524788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,41 +893,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127979097</v>
+        <v>127983115</v>
       </c>
       <c r="B4" t="n">
-        <v>40076</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>214803</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -936,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520012</v>
+        <v>519891</v>
       </c>
       <c r="R4" t="n">
-        <v>6524809</v>
+        <v>6524716</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,11 +976,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1430,41 +1429,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127986450</v>
+        <v>127979097</v>
       </c>
       <c r="B9" t="n">
-        <v>92667</v>
+        <v>40076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>214803</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1472,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519639</v>
+        <v>520012</v>
       </c>
       <c r="R9" t="n">
-        <v>6524788</v>
+        <v>6524809</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1510,13 +1511,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1535,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127983115</v>
+        <v>127948538</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,35 +1551,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519891</v>
+        <v>520098</v>
       </c>
       <c r="R10" t="n">
-        <v>6524716</v>
+        <v>6524835</v>
       </c>
       <c r="S10" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127948647</v>
+        <v>127981103</v>
       </c>
       <c r="B12" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520100</v>
+        <v>519953</v>
       </c>
       <c r="R12" t="n">
-        <v>6524842</v>
+        <v>6524860</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,11 +1836,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127949128</v>
+        <v>127988511</v>
       </c>
       <c r="B13" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520070</v>
+        <v>519885</v>
       </c>
       <c r="R13" t="n">
-        <v>6524851</v>
+        <v>6524640</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1949,17 +1944,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1978,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127981103</v>
+        <v>127948647</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519953</v>
+        <v>520100</v>
       </c>
       <c r="R14" t="n">
-        <v>6524860</v>
+        <v>6524842</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2058,6 +2049,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127988511</v>
+        <v>127949128</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519885</v>
+        <v>520070</v>
       </c>
       <c r="R15" t="n">
-        <v>6524640</v>
+        <v>6524851</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2166,13 +2162,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127979875</v>
+        <v>127985911</v>
       </c>
       <c r="B16" t="n">
-        <v>96069</v>
+        <v>40076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,31 +2202,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519924</v>
+        <v>519623</v>
       </c>
       <c r="R16" t="n">
-        <v>6524793</v>
+        <v>6524788</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2249,7 +2250,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2259,7 +2260,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2272,12 +2273,18 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,7 +2303,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127985911</v>
+        <v>127978774</v>
       </c>
       <c r="B17" t="n">
         <v>40076</v>
@@ -2340,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519623</v>
+        <v>520015</v>
       </c>
       <c r="R17" t="n">
-        <v>6524788</v>
+        <v>6524853</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2355,7 +2362,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2365,7 +2372,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2389,7 +2396,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127978774</v>
+        <v>127979875</v>
       </c>
       <c r="B18" t="n">
-        <v>40076</v>
+        <v>96070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,32 +2425,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520015</v>
+        <v>519924</v>
       </c>
       <c r="R18" t="n">
-        <v>6524853</v>
+        <v>6524793</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2488,11 +2493,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3707,7 +3707,7 @@
         <v>127988256</v>
       </c>
       <c r="B30" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R31" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,7 +3898,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3917,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3961,10 +3960,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R32" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4005,6 +4004,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4342,41 +4342,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127986395</v>
+        <v>127987059</v>
       </c>
       <c r="B36" t="n">
-        <v>92631</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519639</v>
+        <v>519688</v>
       </c>
       <c r="R36" t="n">
-        <v>6524788</v>
+        <v>6524694</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4447,43 +4449,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B37" t="n">
-        <v>40076</v>
+        <v>92632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R37" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4529,17 +4529,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127987059</v>
+        <v>127950052</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4569,21 +4565,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4602,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519688</v>
+        <v>520044</v>
       </c>
       <c r="R38" t="n">
-        <v>6524694</v>
+        <v>6524903</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4640,13 +4636,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127978914</v>
+        <v>127986860</v>
       </c>
       <c r="B39" t="n">
-        <v>92639</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,30 +4676,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4707,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520021</v>
+        <v>519744</v>
       </c>
       <c r="R39" t="n">
-        <v>6524832</v>
+        <v>6524735</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4751,6 +4753,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4876,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127986860</v>
+        <v>127978914</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,32 +4890,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4920,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519744</v>
+        <v>520021</v>
       </c>
       <c r="R41" t="n">
-        <v>6524735</v>
+        <v>6524832</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4964,7 +4965,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127983788</v>
+        <v>127981664</v>
       </c>
       <c r="B42" t="n">
-        <v>96069</v>
+        <v>4773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,31 +4994,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519717</v>
+        <v>519843</v>
       </c>
       <c r="R42" t="n">
-        <v>6524808</v>
+        <v>6524831</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5089,10 +5090,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127981664</v>
+        <v>127982266</v>
       </c>
       <c r="B43" t="n">
-        <v>4773</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5100,21 +5101,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519843</v>
+        <v>519814</v>
       </c>
       <c r="R43" t="n">
-        <v>6524831</v>
+        <v>6524877</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5196,10 +5197,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127979704</v>
+        <v>127980473</v>
       </c>
       <c r="B44" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,21 +5208,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5240,10 +5241,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519952</v>
+        <v>519985</v>
       </c>
       <c r="R44" t="n">
-        <v>6524773</v>
+        <v>6524831</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5276,11 +5277,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5307,10 +5303,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127982266</v>
+        <v>127983788</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>96070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,32 +5314,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5351,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519814</v>
+        <v>519717</v>
       </c>
       <c r="R45" t="n">
-        <v>6524877</v>
+        <v>6524808</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5414,10 +5409,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127980473</v>
+        <v>127979704</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5425,21 +5420,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5458,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519985</v>
+        <v>519952</v>
       </c>
       <c r="R46" t="n">
-        <v>6524831</v>
+        <v>6524773</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5494,6 +5489,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,41 +5520,43 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127984700</v>
+        <v>127985707</v>
       </c>
       <c r="B47" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5562,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519633</v>
+        <v>519596</v>
       </c>
       <c r="R47" t="n">
-        <v>6524919</v>
+        <v>6524811</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5577,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5587,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5625,43 +5627,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127980279</v>
+        <v>127984700</v>
       </c>
       <c r="B48" t="n">
-        <v>40076</v>
+        <v>81004</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>214803</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519975</v>
+        <v>519633</v>
       </c>
       <c r="R48" t="n">
-        <v>6524804</v>
+        <v>6524919</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5707,17 +5707,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5736,10 +5732,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5747,21 +5743,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5780,10 +5776,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R49" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5795,7 +5791,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5805,7 +5801,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5818,13 +5814,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6916,45 +6916,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127980871</v>
+        <v>127985560</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6962,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519964</v>
+        <v>519553</v>
       </c>
       <c r="R60" t="n">
-        <v>6524859</v>
+        <v>6524821</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6977,7 +6975,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6987,7 +6985,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -7000,17 +6998,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>på tall</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7029,10 +7023,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985560</v>
+        <v>127985115</v>
       </c>
       <c r="B61" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7040,21 +7034,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7073,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519553</v>
+        <v>519590</v>
       </c>
       <c r="R61" t="n">
-        <v>6524821</v>
+        <v>6524878</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7136,7 +7130,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127985115</v>
+        <v>127980055</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7180,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519590</v>
+        <v>519943</v>
       </c>
       <c r="R62" t="n">
-        <v>6524878</v>
+        <v>6524799</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7195,7 +7189,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7205,7 +7199,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7224,7 +7218,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7243,43 +7236,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980055</v>
+        <v>127980871</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7287,10 +7282,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519943</v>
+        <v>519964</v>
       </c>
       <c r="R63" t="n">
-        <v>6524799</v>
+        <v>6524859</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7323,6 +7318,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B64" t="n">
-        <v>96069</v>
+        <v>8439</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,31 +7360,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7392,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R64" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7455,10 +7456,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B65" t="n">
-        <v>8439</v>
+        <v>96070</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7466,32 +7467,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R65" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -1002,43 +1002,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986585</v>
+        <v>127948538</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519663</v>
+        <v>520098</v>
       </c>
       <c r="R5" t="n">
-        <v>6524783</v>
+        <v>6524835</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1088,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127988398</v>
+        <v>127986585</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1153,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519897</v>
+        <v>519663</v>
       </c>
       <c r="R6" t="n">
-        <v>6524632</v>
+        <v>6524783</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127981516</v>
+        <v>127988398</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1260,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519856</v>
+        <v>519897</v>
       </c>
       <c r="R7" t="n">
-        <v>6524816</v>
+        <v>6524632</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1323,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127980622</v>
+        <v>127981516</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1367,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519968</v>
+        <v>519856</v>
       </c>
       <c r="R8" t="n">
-        <v>6524851</v>
+        <v>6524816</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1411,6 +1408,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127979097</v>
+        <v>127980622</v>
       </c>
       <c r="B9" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520012</v>
+        <v>519968</v>
       </c>
       <c r="R9" t="n">
-        <v>6524809</v>
+        <v>6524851</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1509,11 +1507,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,41 +1533,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127948538</v>
+        <v>127979097</v>
       </c>
       <c r="B10" t="n">
-        <v>79647</v>
+        <v>40076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>214803</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520098</v>
+        <v>520012</v>
       </c>
       <c r="R10" t="n">
-        <v>6524835</v>
+        <v>6524809</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127985911</v>
+        <v>127979875</v>
       </c>
       <c r="B16" t="n">
-        <v>40076</v>
+        <v>96070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,32 +2202,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2235,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519623</v>
+        <v>519924</v>
       </c>
       <c r="R16" t="n">
-        <v>6524788</v>
+        <v>6524793</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2250,7 +2249,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2260,7 +2259,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2273,18 +2272,12 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2303,7 +2296,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127978774</v>
+        <v>127985911</v>
       </c>
       <c r="B17" t="n">
         <v>40076</v>
@@ -2347,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520015</v>
+        <v>519623</v>
       </c>
       <c r="R17" t="n">
-        <v>6524853</v>
+        <v>6524788</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2362,7 +2355,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2372,7 +2365,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2396,6 +2389,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127979875</v>
+        <v>127978774</v>
       </c>
       <c r="B18" t="n">
-        <v>96070</v>
+        <v>40076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,31 +2419,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519924</v>
+        <v>520015</v>
       </c>
       <c r="R18" t="n">
-        <v>6524793</v>
+        <v>6524853</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2493,6 +2488,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,41 +2626,44 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127982168</v>
+        <v>127983089</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2670,13 +2673,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519819</v>
+        <v>519891</v>
       </c>
       <c r="R20" t="n">
-        <v>6524878</v>
+        <v>6524716</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,7 +2717,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,7 +2735,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982418</v>
+        <v>127982168</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2777,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519808</v>
+        <v>519819</v>
       </c>
       <c r="R21" t="n">
-        <v>6524877</v>
+        <v>6524878</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2840,44 +2842,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127983089</v>
+        <v>127982418</v>
       </c>
       <c r="B22" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2887,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519891</v>
+        <v>519808</v>
       </c>
       <c r="R22" t="n">
-        <v>6524716</v>
+        <v>6524877</v>
       </c>
       <c r="S22" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2931,6 +2930,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127982588</v>
+        <v>127949748</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519798</v>
+        <v>520046</v>
       </c>
       <c r="R25" t="n">
-        <v>6524851</v>
+        <v>6524882</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,7 +3260,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3279,7 +3278,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127950272</v>
+        <v>127982588</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3323,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520031</v>
+        <v>519798</v>
       </c>
       <c r="R26" t="n">
-        <v>6524880</v>
+        <v>6524851</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3367,6 +3366,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950402</v>
+        <v>127950272</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520020</v>
+        <v>520031</v>
       </c>
       <c r="R27" t="n">
-        <v>6524923</v>
+        <v>6524880</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127949748</v>
+        <v>127950402</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520046</v>
+        <v>520020</v>
       </c>
       <c r="R28" t="n">
-        <v>6524882</v>
+        <v>6524923</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127984194</v>
+        <v>127988256</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>96070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,32 +3608,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3641,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519680</v>
+        <v>519889</v>
       </c>
       <c r="R29" t="n">
-        <v>6524874</v>
+        <v>6524614</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3704,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127988256</v>
+        <v>127984194</v>
       </c>
       <c r="B30" t="n">
-        <v>96070</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,31 +3714,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519889</v>
+        <v>519680</v>
       </c>
       <c r="R30" t="n">
-        <v>6524614</v>
+        <v>6524874</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127948726</v>
+        <v>127987178</v>
       </c>
       <c r="B33" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +4034,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520092</v>
+        <v>519677</v>
       </c>
       <c r="R33" t="n">
-        <v>6524842</v>
+        <v>6524696</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,6 +4111,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948430</v>
+        <v>127948726</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,21 +4141,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4173,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520103</v>
+        <v>520092</v>
       </c>
       <c r="R34" t="n">
-        <v>6524835</v>
+        <v>6524842</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,7 +4236,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127987178</v>
+        <v>127948430</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4279,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519677</v>
+        <v>520103</v>
       </c>
       <c r="R35" t="n">
-        <v>6524696</v>
+        <v>6524835</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4323,7 +4324,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127986860</v>
+        <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,32 +4676,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4709,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519744</v>
+        <v>520021</v>
       </c>
       <c r="R39" t="n">
-        <v>6524735</v>
+        <v>6524832</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4753,7 +4751,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4879,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127978914</v>
+        <v>127986860</v>
       </c>
       <c r="B41" t="n">
-        <v>92640</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,30 +4887,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4921,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520021</v>
+        <v>519744</v>
       </c>
       <c r="R41" t="n">
-        <v>6524832</v>
+        <v>6524735</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4965,6 +4964,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127981664</v>
+        <v>127982266</v>
       </c>
       <c r="B42" t="n">
-        <v>4773</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519843</v>
+        <v>519814</v>
       </c>
       <c r="R42" t="n">
-        <v>6524831</v>
+        <v>6524877</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5090,10 +5090,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127982266</v>
+        <v>127983788</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>96070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,32 +5101,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5134,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519814</v>
+        <v>519717</v>
       </c>
       <c r="R43" t="n">
-        <v>6524877</v>
+        <v>6524808</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5303,10 +5302,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127983788</v>
+        <v>127981664</v>
       </c>
       <c r="B45" t="n">
-        <v>96070</v>
+        <v>4773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5314,31 +5313,32 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519717</v>
+        <v>519843</v>
       </c>
       <c r="R45" t="n">
-        <v>6524808</v>
+        <v>6524831</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,21 +5531,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R47" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5602,13 +5602,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5732,10 +5736,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B49" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5743,21 +5747,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5776,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R49" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5791,7 +5795,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5801,7 +5805,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5814,17 +5818,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>8439</v>
+        <v>96070</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,32 +7360,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7393,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R64" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7456,10 +7455,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B65" t="n">
-        <v>96070</v>
+        <v>8439</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,31 +7466,32 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R65" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127986450</v>
+        <v>127948538</v>
       </c>
       <c r="B3" t="n">
-        <v>92668</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,27 +799,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519639</v>
+        <v>520098</v>
       </c>
       <c r="R3" t="n">
-        <v>6524788</v>
+        <v>6524835</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1002,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127948538</v>
+        <v>127986450</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>92669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,27 +1012,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1044,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520098</v>
+        <v>519639</v>
       </c>
       <c r="R5" t="n">
-        <v>6524835</v>
+        <v>6524788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127981103</v>
+        <v>127948647</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519953</v>
+        <v>520100</v>
       </c>
       <c r="R12" t="n">
-        <v>6524860</v>
+        <v>6524842</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,6 +1836,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127988511</v>
+        <v>127949128</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519885</v>
+        <v>520070</v>
       </c>
       <c r="R13" t="n">
-        <v>6524640</v>
+        <v>6524851</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1944,13 +1949,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127948647</v>
+        <v>127981103</v>
       </c>
       <c r="B14" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1989,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520100</v>
+        <v>519953</v>
       </c>
       <c r="R14" t="n">
-        <v>6524842</v>
+        <v>6524860</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2049,11 +2058,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127949128</v>
+        <v>127988511</v>
       </c>
       <c r="B15" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520070</v>
+        <v>519885</v>
       </c>
       <c r="R15" t="n">
-        <v>6524851</v>
+        <v>6524640</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2162,17 +2166,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>127979875</v>
       </c>
       <c r="B16" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2626,44 +2626,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127983089</v>
+        <v>127982168</v>
       </c>
       <c r="B20" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2673,13 +2670,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519891</v>
+        <v>519819</v>
       </c>
       <c r="R20" t="n">
-        <v>6524716</v>
+        <v>6524878</v>
       </c>
       <c r="S20" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2717,6 +2714,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2735,7 +2733,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982168</v>
+        <v>127982418</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2779,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519819</v>
+        <v>519808</v>
       </c>
       <c r="R21" t="n">
-        <v>6524878</v>
+        <v>6524877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2842,41 +2840,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127982418</v>
+        <v>127983089</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2886,13 +2887,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519808</v>
+        <v>519891</v>
       </c>
       <c r="R22" t="n">
-        <v>6524877</v>
+        <v>6524716</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2931,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127949748</v>
+        <v>127982588</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520046</v>
+        <v>519798</v>
       </c>
       <c r="R25" t="n">
-        <v>6524882</v>
+        <v>6524851</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,6 +3260,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3278,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127982588</v>
+        <v>127950272</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3322,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519798</v>
+        <v>520031</v>
       </c>
       <c r="R26" t="n">
-        <v>6524851</v>
+        <v>6524880</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3366,7 +3367,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950272</v>
+        <v>127950402</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520031</v>
+        <v>520020</v>
       </c>
       <c r="R27" t="n">
-        <v>6524880</v>
+        <v>6524923</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127950402</v>
+        <v>127949748</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520020</v>
+        <v>520046</v>
       </c>
       <c r="R28" t="n">
-        <v>6524923</v>
+        <v>6524882</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127988256</v>
+        <v>127984194</v>
       </c>
       <c r="B29" t="n">
-        <v>96070</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,31 +3608,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3640,10 +3641,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519889</v>
+        <v>519680</v>
       </c>
       <c r="R29" t="n">
-        <v>6524614</v>
+        <v>6524874</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3703,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127984194</v>
+        <v>127988256</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>96071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3714,32 +3715,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519680</v>
+        <v>519889</v>
       </c>
       <c r="R30" t="n">
-        <v>6524874</v>
+        <v>6524614</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R31" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,6 +3898,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3916,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3960,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R32" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4004,7 +4005,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127987178</v>
+        <v>127948726</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +4034,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519677</v>
+        <v>520092</v>
       </c>
       <c r="R33" t="n">
-        <v>6524696</v>
+        <v>6524842</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,7 +4111,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4130,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948726</v>
+        <v>127948430</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,21 +4140,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520092</v>
+        <v>520103</v>
       </c>
       <c r="R34" t="n">
-        <v>6524842</v>
+        <v>6524835</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4236,7 +4235,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127948430</v>
+        <v>127987178</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4280,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520103</v>
+        <v>519677</v>
       </c>
       <c r="R35" t="n">
-        <v>6524835</v>
+        <v>6524696</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4324,6 +4323,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4342,10 +4342,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127987059</v>
+        <v>127950052</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,21 +4353,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519688</v>
+        <v>520044</v>
       </c>
       <c r="R36" t="n">
-        <v>6524694</v>
+        <v>6524903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,13 +4424,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4452,7 +4456,7 @@
         <v>127986395</v>
       </c>
       <c r="B37" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4554,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127950052</v>
+        <v>127987059</v>
       </c>
       <c r="B38" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,21 +4569,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520044</v>
+        <v>519688</v>
       </c>
       <c r="R38" t="n">
-        <v>6524903</v>
+        <v>6524694</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,17 +4640,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127978914</v>
+        <v>127988102</v>
       </c>
       <c r="B39" t="n">
-        <v>92640</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,30 +4676,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4707,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520021</v>
+        <v>519876</v>
       </c>
       <c r="R39" t="n">
-        <v>6524832</v>
+        <v>6524610</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4751,6 +4753,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4769,7 +4772,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4813,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R40" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4876,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127986860</v>
+        <v>127978914</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92641</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,32 +4890,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4920,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519744</v>
+        <v>520021</v>
       </c>
       <c r="R41" t="n">
-        <v>6524735</v>
+        <v>6524832</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4964,7 +4965,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127982266</v>
+        <v>127979704</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519814</v>
+        <v>519952</v>
       </c>
       <c r="R42" t="n">
-        <v>6524877</v>
+        <v>6524773</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5065,13 +5065,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5093,7 +5097,7 @@
         <v>127983788</v>
       </c>
       <c r="B43" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5196,10 +5200,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127980473</v>
+        <v>127981664</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>4773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,21 +5211,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5240,7 +5244,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519985</v>
+        <v>519843</v>
       </c>
       <c r="R44" t="n">
         <v>6524831</v>
@@ -5284,6 +5288,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5302,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127981664</v>
+        <v>127982266</v>
       </c>
       <c r="B45" t="n">
-        <v>4773</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5313,21 +5318,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5351,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519843</v>
+        <v>519814</v>
       </c>
       <c r="R45" t="n">
-        <v>6524831</v>
+        <v>6524877</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5409,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127979704</v>
+        <v>127980473</v>
       </c>
       <c r="B46" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5420,21 +5425,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5453,10 +5458,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519952</v>
+        <v>519985</v>
       </c>
       <c r="R46" t="n">
-        <v>6524773</v>
+        <v>6524831</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5489,11 +5494,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127984457</v>
+        <v>127981257</v>
       </c>
       <c r="B56" t="n">
-        <v>6272</v>
+        <v>79115</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,32 +6502,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105336</v>
+        <v>6450</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6535,10 +6533,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519670</v>
+        <v>519957</v>
       </c>
       <c r="R56" t="n">
-        <v>6524879</v>
+        <v>6524845</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6598,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127979259</v>
+        <v>127984457</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>6272</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6609,32 +6607,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6642,10 +6640,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520006</v>
+        <v>519670</v>
       </c>
       <c r="R57" t="n">
-        <v>6524801</v>
+        <v>6524879</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6686,6 +6684,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6704,7 +6703,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127984642</v>
+        <v>127979259</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6748,10 +6747,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519633</v>
+        <v>520006</v>
       </c>
       <c r="R58" t="n">
-        <v>6524919</v>
+        <v>6524801</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6792,7 +6791,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6811,10 +6809,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127981257</v>
+        <v>127984642</v>
       </c>
       <c r="B59" t="n">
-        <v>79115</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6822,30 +6820,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6450</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519957</v>
+        <v>519633</v>
       </c>
       <c r="R59" t="n">
-        <v>6524845</v>
+        <v>6524919</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6916,43 +6916,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127985560</v>
+        <v>127980871</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6960,10 +6962,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519553</v>
+        <v>519964</v>
       </c>
       <c r="R60" t="n">
-        <v>6524821</v>
+        <v>6524859</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6975,7 +6977,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6985,7 +6987,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -6998,13 +7000,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>på tall</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7023,10 +7029,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985115</v>
+        <v>127985560</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7034,21 +7040,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7073,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519590</v>
+        <v>519553</v>
       </c>
       <c r="R61" t="n">
-        <v>6524878</v>
+        <v>6524821</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7130,7 +7136,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127980055</v>
+        <v>127985115</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7174,10 +7180,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519943</v>
+        <v>519590</v>
       </c>
       <c r="R62" t="n">
-        <v>6524799</v>
+        <v>6524878</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7189,7 +7195,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7199,7 +7205,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7218,6 +7224,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7236,45 +7243,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980871</v>
+        <v>127980055</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7282,10 +7287,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519964</v>
+        <v>519943</v>
       </c>
       <c r="R63" t="n">
-        <v>6524859</v>
+        <v>6524799</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7318,11 +7323,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7352,7 +7352,7 @@
         <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127948538</v>
+        <v>127986450</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>92670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,27 +799,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520098</v>
+        <v>519639</v>
       </c>
       <c r="R3" t="n">
-        <v>6524835</v>
+        <v>6524788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1001,41 +1002,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986450</v>
+        <v>127981516</v>
       </c>
       <c r="B5" t="n">
-        <v>92669</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519639</v>
+        <v>519856</v>
       </c>
       <c r="R5" t="n">
-        <v>6524788</v>
+        <v>6524816</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1320,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127981516</v>
+        <v>127980622</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1364,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519856</v>
+        <v>519968</v>
       </c>
       <c r="R8" t="n">
-        <v>6524816</v>
+        <v>6524851</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1408,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127980622</v>
+        <v>127979097</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519968</v>
+        <v>520012</v>
       </c>
       <c r="R9" t="n">
-        <v>6524851</v>
+        <v>6524809</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1507,6 +1509,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,43 +1540,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127979097</v>
+        <v>127948538</v>
       </c>
       <c r="B10" t="n">
-        <v>40076</v>
+        <v>79647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>214803</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520012</v>
+        <v>520098</v>
       </c>
       <c r="R10" t="n">
-        <v>6524809</v>
+        <v>6524835</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127948647</v>
+        <v>127988511</v>
       </c>
       <c r="B12" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520100</v>
+        <v>519885</v>
       </c>
       <c r="R12" t="n">
-        <v>6524842</v>
+        <v>6524640</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1838,17 +1838,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1867,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127949128</v>
+        <v>127981103</v>
       </c>
       <c r="B13" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1874,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520070</v>
+        <v>519953</v>
       </c>
       <c r="R13" t="n">
-        <v>6524851</v>
+        <v>6524860</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1947,11 +1943,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127981103</v>
+        <v>127948647</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519953</v>
+        <v>520100</v>
       </c>
       <c r="R14" t="n">
-        <v>6524860</v>
+        <v>6524842</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2058,6 +2049,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127988511</v>
+        <v>127949128</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519885</v>
+        <v>520070</v>
       </c>
       <c r="R15" t="n">
-        <v>6524640</v>
+        <v>6524851</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2166,13 +2162,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>127979875</v>
       </c>
       <c r="B16" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127982588</v>
+        <v>127950272</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519798</v>
+        <v>520031</v>
       </c>
       <c r="R25" t="n">
-        <v>6524851</v>
+        <v>6524880</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,7 +3260,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3279,7 +3278,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127950272</v>
+        <v>127950402</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3323,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520031</v>
+        <v>520020</v>
       </c>
       <c r="R26" t="n">
-        <v>6524880</v>
+        <v>6524923</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3385,7 +3384,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950402</v>
+        <v>127982588</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3429,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520020</v>
+        <v>519798</v>
       </c>
       <c r="R27" t="n">
-        <v>6524923</v>
+        <v>6524851</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3473,6 +3472,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127984194</v>
+        <v>127988256</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>96072</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,32 +3608,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3641,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519680</v>
+        <v>519889</v>
       </c>
       <c r="R29" t="n">
-        <v>6524874</v>
+        <v>6524614</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3704,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127988256</v>
+        <v>127984194</v>
       </c>
       <c r="B30" t="n">
-        <v>96071</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,31 +3714,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519889</v>
+        <v>519680</v>
       </c>
       <c r="R30" t="n">
-        <v>6524614</v>
+        <v>6524874</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4342,43 +4342,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>40076</v>
+        <v>92634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R36" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,17 +4422,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,41 +4447,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127986395</v>
+        <v>127987059</v>
       </c>
       <c r="B37" t="n">
-        <v>92633</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4495,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519639</v>
+        <v>519688</v>
       </c>
       <c r="R37" t="n">
-        <v>6524788</v>
+        <v>6524694</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127987059</v>
+        <v>127950052</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4569,21 +4565,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4602,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519688</v>
+        <v>520044</v>
       </c>
       <c r="R38" t="n">
-        <v>6524694</v>
+        <v>6524903</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4640,13 +4636,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127988102</v>
+        <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,32 +4676,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4709,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519876</v>
+        <v>520021</v>
       </c>
       <c r="R39" t="n">
-        <v>6524610</v>
+        <v>6524832</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4753,7 +4751,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4772,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127986860</v>
+        <v>127988102</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4816,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519744</v>
+        <v>519876</v>
       </c>
       <c r="R40" t="n">
-        <v>6524735</v>
+        <v>6524610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4879,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127978914</v>
+        <v>127986860</v>
       </c>
       <c r="B41" t="n">
-        <v>92641</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,30 +4887,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4921,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520021</v>
+        <v>519744</v>
       </c>
       <c r="R41" t="n">
-        <v>6524832</v>
+        <v>6524735</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4965,6 +4964,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127979704</v>
+        <v>127983788</v>
       </c>
       <c r="B42" t="n">
-        <v>40076</v>
+        <v>96072</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,32 +4994,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519952</v>
+        <v>519717</v>
       </c>
       <c r="R42" t="n">
-        <v>6524773</v>
+        <v>6524808</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5065,17 +5064,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5094,10 +5089,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127983788</v>
+        <v>127982266</v>
       </c>
       <c r="B43" t="n">
-        <v>96071</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5105,31 +5100,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5137,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519717</v>
+        <v>519814</v>
       </c>
       <c r="R43" t="n">
-        <v>6524808</v>
+        <v>6524877</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5200,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127981664</v>
+        <v>127980473</v>
       </c>
       <c r="B44" t="n">
-        <v>4773</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,21 +5207,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5244,7 +5240,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519843</v>
+        <v>519985</v>
       </c>
       <c r="R44" t="n">
         <v>6524831</v>
@@ -5288,7 +5284,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5307,10 +5302,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127982266</v>
+        <v>127979704</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,21 +5313,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5351,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519814</v>
+        <v>519952</v>
       </c>
       <c r="R45" t="n">
-        <v>6524877</v>
+        <v>6524773</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5389,13 +5384,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127980473</v>
+        <v>127981664</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>4773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5425,21 +5424,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5458,7 +5457,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519985</v>
+        <v>519843</v>
       </c>
       <c r="R46" t="n">
         <v>6524831</v>
@@ -5502,6 +5501,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B47" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,21 +5531,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R47" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5602,17 +5602,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,41 +5627,43 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127984700</v>
+        <v>127980279</v>
       </c>
       <c r="B48" t="n">
-        <v>81004</v>
+        <v>40076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>214803</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5673,10 +5671,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519633</v>
+        <v>519975</v>
       </c>
       <c r="R48" t="n">
-        <v>6524919</v>
+        <v>6524804</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5711,13 +5709,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5736,43 +5738,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127985707</v>
+        <v>127984700</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>81004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519596</v>
+        <v>519633</v>
       </c>
       <c r="R49" t="n">
-        <v>6524811</v>
+        <v>6524919</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127949357</v>
+        <v>127950593</v>
       </c>
       <c r="B50" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520055</v>
+        <v>519991</v>
       </c>
       <c r="R50" t="n">
-        <v>6524858</v>
+        <v>6524893</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,11 +5923,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127949218</v>
+        <v>127979471</v>
       </c>
       <c r="B51" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520067</v>
+        <v>519986</v>
       </c>
       <c r="R51" t="n">
-        <v>6524857</v>
+        <v>6524777</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6034,11 +6029,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6065,10 +6055,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127950593</v>
+        <v>127983540</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6076,21 +6066,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6109,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519991</v>
+        <v>519733</v>
       </c>
       <c r="R52" t="n">
-        <v>6524893</v>
+        <v>6524792</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6153,6 +6143,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6162,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127979471</v>
+        <v>127987902</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,21 +6173,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6215,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519986</v>
+        <v>519738</v>
       </c>
       <c r="R53" t="n">
-        <v>6524777</v>
+        <v>6524605</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6259,6 +6250,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6277,10 +6269,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127987902</v>
+        <v>127949357</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,21 +6280,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6321,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519738</v>
+        <v>520055</v>
       </c>
       <c r="R54" t="n">
-        <v>6524605</v>
+        <v>6524858</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6359,13 +6351,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6384,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127983540</v>
+        <v>127949218</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6395,21 +6391,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6428,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519733</v>
+        <v>520067</v>
       </c>
       <c r="R55" t="n">
-        <v>6524792</v>
+        <v>6524857</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6466,13 +6462,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127984457</v>
+        <v>127979259</v>
       </c>
       <c r="B57" t="n">
-        <v>6272</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,32 +6607,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519670</v>
+        <v>520006</v>
       </c>
       <c r="R57" t="n">
-        <v>6524879</v>
+        <v>6524801</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6684,7 +6684,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6703,7 +6702,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127979259</v>
+        <v>127984642</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6747,10 +6746,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520006</v>
+        <v>519633</v>
       </c>
       <c r="R58" t="n">
-        <v>6524801</v>
+        <v>6524919</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6791,6 +6790,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127984642</v>
+        <v>127984457</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>6272</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6820,32 +6820,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519633</v>
+        <v>519670</v>
       </c>
       <c r="R59" t="n">
-        <v>6524919</v>
+        <v>6524879</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7352,7 +7352,7 @@
         <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127981516</v>
+        <v>127986585</v>
       </c>
       <c r="B5" t="n">
         <v>8450</v>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519856</v>
+        <v>519663</v>
       </c>
       <c r="R5" t="n">
-        <v>6524816</v>
+        <v>6524783</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127986585</v>
+        <v>127988398</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519663</v>
+        <v>519897</v>
       </c>
       <c r="R6" t="n">
-        <v>6524783</v>
+        <v>6524632</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127988398</v>
+        <v>127981516</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519897</v>
+        <v>519856</v>
       </c>
       <c r="R7" t="n">
-        <v>6524632</v>
+        <v>6524816</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1429,43 +1429,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127979097</v>
+        <v>127948538</v>
       </c>
       <c r="B9" t="n">
-        <v>40076</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>214803</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1473,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520012</v>
+        <v>520098</v>
       </c>
       <c r="R9" t="n">
-        <v>6524809</v>
+        <v>6524835</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1509,11 +1507,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,41 +1533,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127948538</v>
+        <v>127979097</v>
       </c>
       <c r="B10" t="n">
-        <v>79647</v>
+        <v>40076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>214803</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520098</v>
+        <v>520012</v>
       </c>
       <c r="R10" t="n">
-        <v>6524835</v>
+        <v>6524809</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127988511</v>
+        <v>127981103</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519885</v>
+        <v>519953</v>
       </c>
       <c r="R12" t="n">
-        <v>6524640</v>
+        <v>6524860</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1844,7 +1844,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127981103</v>
+        <v>127988511</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1907,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519953</v>
+        <v>519885</v>
       </c>
       <c r="R13" t="n">
-        <v>6524860</v>
+        <v>6524640</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1951,6 +1950,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2626,41 +2626,44 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127982168</v>
+        <v>127983089</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2670,13 +2673,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519819</v>
+        <v>519891</v>
       </c>
       <c r="R20" t="n">
-        <v>6524878</v>
+        <v>6524716</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,7 +2717,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,7 +2735,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982418</v>
+        <v>127982168</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2777,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519808</v>
+        <v>519819</v>
       </c>
       <c r="R21" t="n">
-        <v>6524877</v>
+        <v>6524878</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2840,44 +2842,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127983089</v>
+        <v>127982418</v>
       </c>
       <c r="B22" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2887,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519891</v>
+        <v>519808</v>
       </c>
       <c r="R22" t="n">
-        <v>6524716</v>
+        <v>6524877</v>
       </c>
       <c r="S22" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2931,6 +2930,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127950272</v>
+        <v>127982588</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520031</v>
+        <v>519798</v>
       </c>
       <c r="R25" t="n">
-        <v>6524880</v>
+        <v>6524851</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,6 +3260,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3278,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127950402</v>
+        <v>127950272</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3322,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520020</v>
+        <v>520031</v>
       </c>
       <c r="R26" t="n">
-        <v>6524923</v>
+        <v>6524880</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3384,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127982588</v>
+        <v>127950402</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3428,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519798</v>
+        <v>520020</v>
       </c>
       <c r="R27" t="n">
-        <v>6524851</v>
+        <v>6524923</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3472,7 +3473,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R31" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,7 +3898,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3917,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3961,10 +3960,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R32" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4005,6 +4004,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127948726</v>
+        <v>127948430</v>
       </c>
       <c r="B33" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +4034,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520092</v>
+        <v>520103</v>
       </c>
       <c r="R33" t="n">
-        <v>6524842</v>
+        <v>6524835</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948430</v>
+        <v>127948726</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,21 +4140,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520103</v>
+        <v>520092</v>
       </c>
       <c r="R34" t="n">
-        <v>6524835</v>
+        <v>6524842</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127978914</v>
+        <v>127988102</v>
       </c>
       <c r="B39" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,30 +4676,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4707,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520021</v>
+        <v>519876</v>
       </c>
       <c r="R39" t="n">
-        <v>6524832</v>
+        <v>6524610</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4751,6 +4753,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4769,7 +4772,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4813,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R40" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4876,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127986860</v>
+        <v>127978914</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,32 +4890,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4920,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519744</v>
+        <v>520021</v>
       </c>
       <c r="R41" t="n">
-        <v>6524735</v>
+        <v>6524832</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4964,7 +4965,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B42" t="n">
-        <v>96072</v>
+        <v>40076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,31 +4994,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R42" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5064,13 +5065,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5302,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127979704</v>
+        <v>127983788</v>
       </c>
       <c r="B45" t="n">
-        <v>40076</v>
+        <v>96072</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5313,32 +5318,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5346,10 +5350,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519952</v>
+        <v>519717</v>
       </c>
       <c r="R45" t="n">
-        <v>6524773</v>
+        <v>6524808</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5384,17 +5388,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5520,43 +5520,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127985707</v>
+        <v>127984700</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>81004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5564,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519596</v>
+        <v>519633</v>
       </c>
       <c r="R47" t="n">
-        <v>6524811</v>
+        <v>6524919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5577,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5587,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5627,10 +5625,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B48" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5636,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5671,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R48" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5684,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5696,7 +5694,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5709,17 +5707,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,41 +5732,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127984700</v>
+        <v>127980279</v>
       </c>
       <c r="B49" t="n">
-        <v>81004</v>
+        <v>40076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1049</v>
+        <v>214803</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5780,10 +5776,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519633</v>
+        <v>519975</v>
       </c>
       <c r="R49" t="n">
-        <v>6524919</v>
+        <v>6524804</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5818,13 +5814,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127983540</v>
+        <v>127987902</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519733</v>
+        <v>519738</v>
       </c>
       <c r="R52" t="n">
-        <v>6524792</v>
+        <v>6524605</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127987902</v>
+        <v>127983540</v>
       </c>
       <c r="B53" t="n">
         <v>8450</v>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519738</v>
+        <v>519733</v>
       </c>
       <c r="R53" t="n">
-        <v>6524605</v>
+        <v>6524792</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127979259</v>
+        <v>127984457</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>6272</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,32 +6607,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520006</v>
+        <v>519670</v>
       </c>
       <c r="R57" t="n">
-        <v>6524801</v>
+        <v>6524879</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6684,6 +6684,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6702,7 +6703,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127984642</v>
+        <v>127979259</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6746,10 +6747,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519633</v>
+        <v>520006</v>
       </c>
       <c r="R58" t="n">
-        <v>6524919</v>
+        <v>6524801</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6790,7 +6791,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127984457</v>
+        <v>127984642</v>
       </c>
       <c r="B59" t="n">
-        <v>6272</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6820,32 +6820,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519670</v>
+        <v>519633</v>
       </c>
       <c r="R59" t="n">
-        <v>6524879</v>
+        <v>6524919</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,41 +788,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127986450</v>
+        <v>127979097</v>
       </c>
       <c r="B3" t="n">
-        <v>92670</v>
+        <v>40076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>214803</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519639</v>
+        <v>520012</v>
       </c>
       <c r="R3" t="n">
-        <v>6524788</v>
+        <v>6524809</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,13 +870,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127983115</v>
+        <v>127986450</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>92670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,35 +910,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519891</v>
+        <v>519639</v>
       </c>
       <c r="R4" t="n">
-        <v>6524716</v>
+        <v>6524788</v>
       </c>
       <c r="S4" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,6 +985,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,41 +1004,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986585</v>
+        <v>127983115</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1046,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519663</v>
+        <v>519891</v>
       </c>
       <c r="R5" t="n">
-        <v>6524783</v>
+        <v>6524716</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1095,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,43 +1113,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127988398</v>
+        <v>127948538</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519897</v>
+        <v>520098</v>
       </c>
       <c r="R6" t="n">
-        <v>6524632</v>
+        <v>6524835</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1197,7 +1199,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127981516</v>
+        <v>127986585</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1260,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519856</v>
+        <v>519663</v>
       </c>
       <c r="R7" t="n">
-        <v>6524816</v>
+        <v>6524783</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1323,7 +1324,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127980622</v>
+        <v>127988398</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519968</v>
+        <v>519897</v>
       </c>
       <c r="R8" t="n">
-        <v>6524851</v>
+        <v>6524632</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1411,6 +1412,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1429,41 +1431,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127948538</v>
+        <v>127981516</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1471,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520098</v>
+        <v>519856</v>
       </c>
       <c r="R9" t="n">
-        <v>6524835</v>
+        <v>6524816</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1515,6 +1519,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127979097</v>
+        <v>127980622</v>
       </c>
       <c r="B10" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520012</v>
+        <v>519968</v>
       </c>
       <c r="R10" t="n">
-        <v>6524809</v>
+        <v>6524851</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127988102</v>
+        <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,32 +4676,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4709,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519876</v>
+        <v>520021</v>
       </c>
       <c r="R39" t="n">
-        <v>6524610</v>
+        <v>6524832</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4753,7 +4751,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4772,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127986860</v>
+        <v>127988102</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4816,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519744</v>
+        <v>519876</v>
       </c>
       <c r="R40" t="n">
-        <v>6524735</v>
+        <v>6524610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4879,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127978914</v>
+        <v>127986860</v>
       </c>
       <c r="B41" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,30 +4887,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4921,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520021</v>
+        <v>519744</v>
       </c>
       <c r="R41" t="n">
-        <v>6524832</v>
+        <v>6524735</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4965,6 +4964,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127979704</v>
+        <v>127983788</v>
       </c>
       <c r="B42" t="n">
-        <v>40076</v>
+        <v>96072</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,32 +4994,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519952</v>
+        <v>519717</v>
       </c>
       <c r="R42" t="n">
-        <v>6524773</v>
+        <v>6524808</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5065,17 +5064,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5307,10 +5302,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B45" t="n">
-        <v>96072</v>
+        <v>40076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,31 +5313,32 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5350,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R45" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5388,13 +5384,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127950593</v>
+        <v>127949357</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>40076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519991</v>
+        <v>520055</v>
       </c>
       <c r="R50" t="n">
-        <v>6524893</v>
+        <v>6524858</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,6 +5923,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,10 +5954,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127979471</v>
+        <v>127949218</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>40076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5965,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519986</v>
+        <v>520067</v>
       </c>
       <c r="R51" t="n">
-        <v>6524777</v>
+        <v>6524857</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6029,6 +6034,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6055,10 +6065,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127987902</v>
+        <v>127950593</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,21 +6076,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6109,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519738</v>
+        <v>519991</v>
       </c>
       <c r="R52" t="n">
-        <v>6524605</v>
+        <v>6524893</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6143,7 +6153,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6162,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127983540</v>
+        <v>127979471</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6173,21 +6182,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6215,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519733</v>
+        <v>519986</v>
       </c>
       <c r="R53" t="n">
-        <v>6524792</v>
+        <v>6524777</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6250,7 +6259,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6269,10 +6277,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127949357</v>
+        <v>127987902</v>
       </c>
       <c r="B54" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6280,21 +6288,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6313,10 +6321,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520055</v>
+        <v>519738</v>
       </c>
       <c r="R54" t="n">
-        <v>6524858</v>
+        <v>6524605</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6351,17 +6359,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6380,10 +6384,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127949218</v>
+        <v>127983540</v>
       </c>
       <c r="B55" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,21 +6395,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6428,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520067</v>
+        <v>519733</v>
       </c>
       <c r="R55" t="n">
-        <v>6524857</v>
+        <v>6524792</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6462,17 +6466,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127979875</v>
+        <v>127985911</v>
       </c>
       <c r="B16" t="n">
-        <v>96072</v>
+        <v>40076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,31 +2202,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519924</v>
+        <v>519623</v>
       </c>
       <c r="R16" t="n">
-        <v>6524793</v>
+        <v>6524788</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2249,7 +2250,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2259,7 +2260,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2272,12 +2273,18 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,7 +2303,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127985911</v>
+        <v>127978774</v>
       </c>
       <c r="B17" t="n">
         <v>40076</v>
@@ -2340,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519623</v>
+        <v>520015</v>
       </c>
       <c r="R17" t="n">
-        <v>6524788</v>
+        <v>6524853</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2355,7 +2362,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2365,7 +2372,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2389,7 +2396,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127978774</v>
+        <v>127979875</v>
       </c>
       <c r="B18" t="n">
-        <v>40076</v>
+        <v>96072</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,32 +2425,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520015</v>
+        <v>519924</v>
       </c>
       <c r="R18" t="n">
-        <v>6524853</v>
+        <v>6524793</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2488,11 +2493,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4342,41 +4342,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127986395</v>
+        <v>127950052</v>
       </c>
       <c r="B36" t="n">
-        <v>92634</v>
+        <v>40076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>214803</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519639</v>
+        <v>520044</v>
       </c>
       <c r="R36" t="n">
-        <v>6524788</v>
+        <v>6524903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4422,13 +4424,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,43 +4453,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127987059</v>
+        <v>127986395</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>92634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4491,10 +4495,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519688</v>
+        <v>519639</v>
       </c>
       <c r="R37" t="n">
-        <v>6524694</v>
+        <v>6524788</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4554,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127950052</v>
+        <v>127987059</v>
       </c>
       <c r="B38" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,21 +4569,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520044</v>
+        <v>519688</v>
       </c>
       <c r="R38" t="n">
-        <v>6524903</v>
+        <v>6524694</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,17 +4640,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B42" t="n">
-        <v>96072</v>
+        <v>40076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,31 +4994,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R42" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5064,13 +5065,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5302,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127979704</v>
+        <v>127983788</v>
       </c>
       <c r="B45" t="n">
-        <v>40076</v>
+        <v>96072</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5313,32 +5318,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5346,10 +5350,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519952</v>
+        <v>519717</v>
       </c>
       <c r="R45" t="n">
-        <v>6524773</v>
+        <v>6524808</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5384,17 +5388,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5520,41 +5520,43 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127984700</v>
+        <v>127985707</v>
       </c>
       <c r="B47" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5562,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519633</v>
+        <v>519596</v>
       </c>
       <c r="R47" t="n">
-        <v>6524919</v>
+        <v>6524811</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5577,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5587,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5625,10 +5627,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5636,21 +5638,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5669,10 +5671,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R48" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5684,7 +5686,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5694,7 +5696,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5707,13 +5709,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5732,43 +5738,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127980279</v>
+        <v>127984700</v>
       </c>
       <c r="B49" t="n">
-        <v>40076</v>
+        <v>81004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214803</v>
+        <v>1049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5776,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519975</v>
+        <v>519633</v>
       </c>
       <c r="R49" t="n">
-        <v>6524804</v>
+        <v>6524919</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5814,17 +5818,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127949357</v>
+        <v>127950593</v>
       </c>
       <c r="B50" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520055</v>
+        <v>519991</v>
       </c>
       <c r="R50" t="n">
-        <v>6524858</v>
+        <v>6524893</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,11 +5923,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127949218</v>
+        <v>127979471</v>
       </c>
       <c r="B51" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520067</v>
+        <v>519986</v>
       </c>
       <c r="R51" t="n">
-        <v>6524857</v>
+        <v>6524777</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6034,11 +6029,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6065,10 +6055,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127950593</v>
+        <v>127987902</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6076,21 +6066,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6109,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519991</v>
+        <v>519738</v>
       </c>
       <c r="R52" t="n">
-        <v>6524893</v>
+        <v>6524605</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6153,6 +6143,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6162,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127979471</v>
+        <v>127983540</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,21 +6173,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6215,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519986</v>
+        <v>519733</v>
       </c>
       <c r="R53" t="n">
-        <v>6524777</v>
+        <v>6524792</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6259,6 +6250,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6277,10 +6269,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127987902</v>
+        <v>127949357</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,21 +6280,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6321,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519738</v>
+        <v>520055</v>
       </c>
       <c r="R54" t="n">
-        <v>6524605</v>
+        <v>6524858</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6359,13 +6351,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6384,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127983540</v>
+        <v>127949218</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6395,21 +6391,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6428,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519733</v>
+        <v>520067</v>
       </c>
       <c r="R55" t="n">
-        <v>6524792</v>
+        <v>6524857</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6466,13 +6462,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,43 +788,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127979097</v>
+        <v>127986450</v>
       </c>
       <c r="B3" t="n">
-        <v>40076</v>
+        <v>92670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>214803</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520012</v>
+        <v>519639</v>
       </c>
       <c r="R3" t="n">
-        <v>6524809</v>
+        <v>6524788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,17 +868,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127986450</v>
+        <v>127983115</v>
       </c>
       <c r="B4" t="n">
-        <v>92670</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,30 +904,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519639</v>
+        <v>519891</v>
       </c>
       <c r="R4" t="n">
-        <v>6524788</v>
+        <v>6524716</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,7 +984,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,44 +1002,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127983115</v>
+        <v>127986585</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1051,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519891</v>
+        <v>519663</v>
       </c>
       <c r="R5" t="n">
-        <v>6524716</v>
+        <v>6524783</v>
       </c>
       <c r="S5" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,6 +1090,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,41 +1109,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127948538</v>
+        <v>127988398</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520098</v>
+        <v>519897</v>
       </c>
       <c r="R6" t="n">
-        <v>6524835</v>
+        <v>6524632</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1199,6 +1197,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127986585</v>
+        <v>127981516</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1261,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519663</v>
+        <v>519856</v>
       </c>
       <c r="R7" t="n">
-        <v>6524783</v>
+        <v>6524816</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127988398</v>
+        <v>127980622</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519897</v>
+        <v>519968</v>
       </c>
       <c r="R8" t="n">
-        <v>6524632</v>
+        <v>6524851</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1431,43 +1429,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127981516</v>
+        <v>127948538</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1475,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519856</v>
+        <v>520098</v>
       </c>
       <c r="R9" t="n">
-        <v>6524816</v>
+        <v>6524835</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1519,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1538,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127980622</v>
+        <v>127979097</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1582,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519968</v>
+        <v>520012</v>
       </c>
       <c r="R10" t="n">
-        <v>6524851</v>
+        <v>6524809</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127985911</v>
+        <v>127979875</v>
       </c>
       <c r="B16" t="n">
-        <v>40076</v>
+        <v>96072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,32 +2202,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2235,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519623</v>
+        <v>519924</v>
       </c>
       <c r="R16" t="n">
-        <v>6524788</v>
+        <v>6524793</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2250,7 +2249,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2260,7 +2259,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2273,18 +2272,12 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2303,7 +2296,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127978774</v>
+        <v>127985911</v>
       </c>
       <c r="B17" t="n">
         <v>40076</v>
@@ -2347,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520015</v>
+        <v>519623</v>
       </c>
       <c r="R17" t="n">
-        <v>6524853</v>
+        <v>6524788</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2362,7 +2355,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2372,7 +2365,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2396,6 +2389,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127979875</v>
+        <v>127978774</v>
       </c>
       <c r="B18" t="n">
-        <v>96072</v>
+        <v>40076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,31 +2419,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519924</v>
+        <v>520015</v>
       </c>
       <c r="R18" t="n">
-        <v>6524793</v>
+        <v>6524853</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2493,6 +2488,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4342,43 +4342,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>40076</v>
+        <v>92634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R36" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,17 +4422,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,41 +4447,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127986395</v>
+        <v>127987059</v>
       </c>
       <c r="B37" t="n">
-        <v>92634</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4495,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519639</v>
+        <v>519688</v>
       </c>
       <c r="R37" t="n">
-        <v>6524788</v>
+        <v>6524694</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127987059</v>
+        <v>127950052</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4569,21 +4565,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4602,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519688</v>
+        <v>520044</v>
       </c>
       <c r="R38" t="n">
-        <v>6524694</v>
+        <v>6524903</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4640,13 +4636,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127978914</v>
+        <v>127988102</v>
       </c>
       <c r="B39" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,30 +4676,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4707,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520021</v>
+        <v>519876</v>
       </c>
       <c r="R39" t="n">
-        <v>6524832</v>
+        <v>6524610</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4751,6 +4753,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4769,7 +4772,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4813,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R40" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4876,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127986860</v>
+        <v>127978914</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,32 +4890,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4920,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519744</v>
+        <v>520021</v>
       </c>
       <c r="R41" t="n">
-        <v>6524735</v>
+        <v>6524832</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4964,7 +4965,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5520,43 +5520,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127985707</v>
+        <v>127984700</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>81004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5564,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519596</v>
+        <v>519633</v>
       </c>
       <c r="R47" t="n">
-        <v>6524811</v>
+        <v>6524919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5577,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5587,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5627,10 +5625,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B48" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5636,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5671,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R48" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5684,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5696,7 +5694,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5709,17 +5707,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,41 +5732,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127984700</v>
+        <v>127980279</v>
       </c>
       <c r="B49" t="n">
-        <v>81004</v>
+        <v>40076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1049</v>
+        <v>214803</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5780,10 +5776,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519633</v>
+        <v>519975</v>
       </c>
       <c r="R49" t="n">
-        <v>6524919</v>
+        <v>6524804</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5818,13 +5814,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R31" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,6 +3898,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3916,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3960,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R32" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4004,7 +4005,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127948430</v>
+        <v>127987178</v>
       </c>
       <c r="B33" t="n">
         <v>8450</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520103</v>
+        <v>519677</v>
       </c>
       <c r="R33" t="n">
-        <v>6524835</v>
+        <v>6524696</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,6 +4111,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948726</v>
+        <v>127948430</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,21 +4141,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4173,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520092</v>
+        <v>520103</v>
       </c>
       <c r="R34" t="n">
-        <v>6524842</v>
+        <v>6524835</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127987178</v>
+        <v>127948726</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,21 +4247,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4279,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519677</v>
+        <v>520092</v>
       </c>
       <c r="R35" t="n">
-        <v>6524696</v>
+        <v>6524842</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4323,7 +4324,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4342,41 +4342,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127986395</v>
+        <v>127950052</v>
       </c>
       <c r="B36" t="n">
-        <v>92634</v>
+        <v>40076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>214803</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519639</v>
+        <v>520044</v>
       </c>
       <c r="R36" t="n">
-        <v>6524788</v>
+        <v>6524903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4422,13 +4424,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,43 +4453,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127987059</v>
+        <v>127986395</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>92634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4491,10 +4495,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519688</v>
+        <v>519639</v>
       </c>
       <c r="R37" t="n">
-        <v>6524694</v>
+        <v>6524788</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4554,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127950052</v>
+        <v>127987059</v>
       </c>
       <c r="B38" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,21 +4569,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520044</v>
+        <v>519688</v>
       </c>
       <c r="R38" t="n">
-        <v>6524903</v>
+        <v>6524694</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,17 +4640,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127988102</v>
+        <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,32 +4676,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4709,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519876</v>
+        <v>520021</v>
       </c>
       <c r="R39" t="n">
-        <v>6524610</v>
+        <v>6524832</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4753,7 +4751,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4772,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127986860</v>
+        <v>127988102</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4816,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519744</v>
+        <v>519876</v>
       </c>
       <c r="R40" t="n">
-        <v>6524735</v>
+        <v>6524610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4879,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127978914</v>
+        <v>127986860</v>
       </c>
       <c r="B41" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,30 +4887,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4921,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520021</v>
+        <v>519744</v>
       </c>
       <c r="R41" t="n">
-        <v>6524832</v>
+        <v>6524735</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4965,6 +4964,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127979875</v>
+        <v>127985911</v>
       </c>
       <c r="B16" t="n">
-        <v>96072</v>
+        <v>40076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,31 +2202,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519924</v>
+        <v>519623</v>
       </c>
       <c r="R16" t="n">
-        <v>6524793</v>
+        <v>6524788</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2249,7 +2250,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2259,7 +2260,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2272,12 +2273,18 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,7 +2303,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127985911</v>
+        <v>127978774</v>
       </c>
       <c r="B17" t="n">
         <v>40076</v>
@@ -2340,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519623</v>
+        <v>520015</v>
       </c>
       <c r="R17" t="n">
-        <v>6524788</v>
+        <v>6524853</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2355,7 +2362,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2365,7 +2372,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2389,7 +2396,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127978774</v>
+        <v>127979875</v>
       </c>
       <c r="B18" t="n">
-        <v>40076</v>
+        <v>96072</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,32 +2425,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520015</v>
+        <v>519924</v>
       </c>
       <c r="R18" t="n">
-        <v>6524853</v>
+        <v>6524793</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2488,11 +2493,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127987178</v>
+        <v>127948430</v>
       </c>
       <c r="B33" t="n">
         <v>8450</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519677</v>
+        <v>520103</v>
       </c>
       <c r="R33" t="n">
-        <v>6524696</v>
+        <v>6524835</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,7 +4111,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4130,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948430</v>
+        <v>127948726</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,21 +4140,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520103</v>
+        <v>520092</v>
       </c>
       <c r="R34" t="n">
-        <v>6524835</v>
+        <v>6524842</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4236,10 +4235,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127948726</v>
+        <v>127987178</v>
       </c>
       <c r="B35" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,21 +4246,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4280,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520092</v>
+        <v>519677</v>
       </c>
       <c r="R35" t="n">
-        <v>6524842</v>
+        <v>6524696</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4324,6 +4323,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4342,43 +4342,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>40076</v>
+        <v>92634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R36" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,17 +4422,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,41 +4447,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127986395</v>
+        <v>127987059</v>
       </c>
       <c r="B37" t="n">
-        <v>92634</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4495,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519639</v>
+        <v>519688</v>
       </c>
       <c r="R37" t="n">
-        <v>6524788</v>
+        <v>6524694</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127987059</v>
+        <v>127950052</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4569,21 +4565,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4602,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519688</v>
+        <v>520044</v>
       </c>
       <c r="R38" t="n">
-        <v>6524694</v>
+        <v>6524903</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4640,13 +4636,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5520,41 +5520,43 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127984700</v>
+        <v>127985707</v>
       </c>
       <c r="B47" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5562,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519633</v>
+        <v>519596</v>
       </c>
       <c r="R47" t="n">
-        <v>6524919</v>
+        <v>6524811</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5577,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5587,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5625,10 +5627,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5636,21 +5638,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5669,10 +5671,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R48" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5684,7 +5686,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5694,7 +5696,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5707,13 +5709,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5732,43 +5738,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127980279</v>
+        <v>127984700</v>
       </c>
       <c r="B49" t="n">
-        <v>40076</v>
+        <v>81004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214803</v>
+        <v>1049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5776,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519975</v>
+        <v>519633</v>
       </c>
       <c r="R49" t="n">
-        <v>6524804</v>
+        <v>6524919</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5814,17 +5818,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B64" t="n">
-        <v>96072</v>
+        <v>8439</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,31 +7360,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7392,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R64" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7455,10 +7456,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B65" t="n">
-        <v>8439</v>
+        <v>96072</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7466,32 +7467,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R65" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -4342,41 +4342,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127986395</v>
+        <v>127950052</v>
       </c>
       <c r="B36" t="n">
-        <v>92634</v>
+        <v>40076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>214803</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519639</v>
+        <v>520044</v>
       </c>
       <c r="R36" t="n">
-        <v>6524788</v>
+        <v>6524903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4422,13 +4424,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,43 +4453,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127987059</v>
+        <v>127986395</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>92634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4491,10 +4495,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519688</v>
+        <v>519639</v>
       </c>
       <c r="R37" t="n">
-        <v>6524694</v>
+        <v>6524788</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4554,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127950052</v>
+        <v>127987059</v>
       </c>
       <c r="B38" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,21 +4569,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520044</v>
+        <v>519688</v>
       </c>
       <c r="R38" t="n">
-        <v>6524903</v>
+        <v>6524694</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,17 +4640,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>127986450</v>
       </c>
       <c r="B3" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127983115</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986585</v>
+        <v>127981516</v>
       </c>
       <c r="B5" t="n">
         <v>8450</v>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519663</v>
+        <v>519856</v>
       </c>
       <c r="R5" t="n">
-        <v>6524783</v>
+        <v>6524816</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127988398</v>
+        <v>127986585</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519897</v>
+        <v>519663</v>
       </c>
       <c r="R6" t="n">
-        <v>6524632</v>
+        <v>6524783</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127981516</v>
+        <v>127988398</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519856</v>
+        <v>519897</v>
       </c>
       <c r="R7" t="n">
-        <v>6524816</v>
+        <v>6524632</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
         <v>127948538</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127981103</v>
+        <v>127988511</v>
       </c>
       <c r="B12" t="n">
         <v>8450</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519953</v>
+        <v>519885</v>
       </c>
       <c r="R12" t="n">
-        <v>6524860</v>
+        <v>6524640</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1844,6 +1844,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1862,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127988511</v>
+        <v>127981103</v>
       </c>
       <c r="B13" t="n">
         <v>8450</v>
@@ -1906,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519885</v>
+        <v>519953</v>
       </c>
       <c r="R13" t="n">
-        <v>6524640</v>
+        <v>6524860</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1950,7 +1951,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127985911</v>
+        <v>127979875</v>
       </c>
       <c r="B16" t="n">
-        <v>40076</v>
+        <v>96080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,32 +2202,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2235,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519623</v>
+        <v>519924</v>
       </c>
       <c r="R16" t="n">
-        <v>6524788</v>
+        <v>6524793</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2250,7 +2249,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2260,7 +2259,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2273,18 +2272,12 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2303,7 +2296,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127978774</v>
+        <v>127985911</v>
       </c>
       <c r="B17" t="n">
         <v>40076</v>
@@ -2347,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520015</v>
+        <v>519623</v>
       </c>
       <c r="R17" t="n">
-        <v>6524853</v>
+        <v>6524788</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2362,7 +2355,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2372,7 +2365,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2396,6 +2389,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127979875</v>
+        <v>127978774</v>
       </c>
       <c r="B18" t="n">
-        <v>96072</v>
+        <v>40076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,31 +2419,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519924</v>
+        <v>520015</v>
       </c>
       <c r="R18" t="n">
-        <v>6524793</v>
+        <v>6524853</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2493,6 +2488,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,44 +2626,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127983089</v>
+        <v>127982418</v>
       </c>
       <c r="B20" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2673,13 +2670,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519891</v>
+        <v>519808</v>
       </c>
       <c r="R20" t="n">
-        <v>6524716</v>
+        <v>6524877</v>
       </c>
       <c r="S20" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2717,6 +2714,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2735,41 +2733,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982168</v>
+        <v>127983089</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2779,13 +2780,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519819</v>
+        <v>519891</v>
       </c>
       <c r="R21" t="n">
-        <v>6524878</v>
+        <v>6524716</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2823,7 +2824,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127982418</v>
+        <v>127982168</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519808</v>
+        <v>519819</v>
       </c>
       <c r="R22" t="n">
-        <v>6524877</v>
+        <v>6524878</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127988256</v>
+        <v>127984194</v>
       </c>
       <c r="B29" t="n">
-        <v>96072</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,31 +3608,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3640,10 +3641,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519889</v>
+        <v>519680</v>
       </c>
       <c r="R29" t="n">
-        <v>6524614</v>
+        <v>6524874</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3703,10 +3704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127984194</v>
+        <v>127988256</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>96080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3714,32 +3715,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519680</v>
+        <v>519889</v>
       </c>
       <c r="R30" t="n">
-        <v>6524874</v>
+        <v>6524614</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R31" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,7 +3898,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3917,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3961,10 +3960,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R32" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4005,6 +4004,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127948430</v>
+        <v>127987178</v>
       </c>
       <c r="B33" t="n">
         <v>8450</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520103</v>
+        <v>519677</v>
       </c>
       <c r="R33" t="n">
-        <v>6524835</v>
+        <v>6524696</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,6 +4111,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4235,7 +4236,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127987178</v>
+        <v>127948430</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4279,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519677</v>
+        <v>520103</v>
       </c>
       <c r="R35" t="n">
-        <v>6524696</v>
+        <v>6524835</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4323,7 +4324,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4342,43 +4342,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>40076</v>
+        <v>92642</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R36" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,17 +4422,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,41 +4447,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127986395</v>
+        <v>127987059</v>
       </c>
       <c r="B37" t="n">
-        <v>92634</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4495,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519639</v>
+        <v>519688</v>
       </c>
       <c r="R37" t="n">
-        <v>6524788</v>
+        <v>6524694</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127987059</v>
+        <v>127950052</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>40076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4569,21 +4565,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4602,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519688</v>
+        <v>520044</v>
       </c>
       <c r="R38" t="n">
-        <v>6524694</v>
+        <v>6524903</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4640,13 +4636,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127979704</v>
+        <v>127983788</v>
       </c>
       <c r="B42" t="n">
-        <v>40076</v>
+        <v>96080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,32 +4994,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519952</v>
+        <v>519717</v>
       </c>
       <c r="R42" t="n">
-        <v>6524773</v>
+        <v>6524808</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5065,17 +5064,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5094,10 +5089,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127982266</v>
+        <v>127981664</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>4773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5105,21 +5100,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5138,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519814</v>
+        <v>519843</v>
       </c>
       <c r="R43" t="n">
-        <v>6524877</v>
+        <v>6524831</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5307,10 +5302,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127983788</v>
+        <v>127982266</v>
       </c>
       <c r="B45" t="n">
-        <v>96072</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,31 +5313,32 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5350,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519717</v>
+        <v>519814</v>
       </c>
       <c r="R45" t="n">
-        <v>6524808</v>
+        <v>6524877</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5413,10 +5409,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127981664</v>
+        <v>127979704</v>
       </c>
       <c r="B46" t="n">
-        <v>4773</v>
+        <v>40076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5424,21 +5420,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100299</v>
+        <v>214803</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5457,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519843</v>
+        <v>519952</v>
       </c>
       <c r="R46" t="n">
-        <v>6524831</v>
+        <v>6524773</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5495,13 +5491,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5520,43 +5520,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127985707</v>
+        <v>127984700</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>81007</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5564,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519596</v>
+        <v>519633</v>
       </c>
       <c r="R47" t="n">
-        <v>6524811</v>
+        <v>6524919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5577,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5587,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5627,10 +5625,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B48" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5636,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5671,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R48" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5684,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5696,7 +5694,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5709,17 +5707,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5738,41 +5732,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127984700</v>
+        <v>127980279</v>
       </c>
       <c r="B49" t="n">
-        <v>81004</v>
+        <v>40076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1049</v>
+        <v>214803</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5780,10 +5776,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519633</v>
+        <v>519975</v>
       </c>
       <c r="R49" t="n">
-        <v>6524919</v>
+        <v>6524804</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5818,13 +5814,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127950593</v>
+        <v>127949357</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>40076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519991</v>
+        <v>520055</v>
       </c>
       <c r="R50" t="n">
-        <v>6524893</v>
+        <v>6524858</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,6 +5923,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,10 +5954,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127979471</v>
+        <v>127949218</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>40076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5965,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519986</v>
+        <v>520067</v>
       </c>
       <c r="R51" t="n">
-        <v>6524777</v>
+        <v>6524857</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6029,6 +6034,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6162,10 +6172,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127983540</v>
+        <v>127979471</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6173,21 +6183,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6216,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519733</v>
+        <v>519986</v>
       </c>
       <c r="R53" t="n">
-        <v>6524792</v>
+        <v>6524777</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6250,7 +6260,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6269,10 +6278,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127949357</v>
+        <v>127983540</v>
       </c>
       <c r="B54" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6280,21 +6289,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6313,10 +6322,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520055</v>
+        <v>519733</v>
       </c>
       <c r="R54" t="n">
-        <v>6524858</v>
+        <v>6524792</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6351,17 +6360,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6380,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127949218</v>
+        <v>127950593</v>
       </c>
       <c r="B55" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6429,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520067</v>
+        <v>519991</v>
       </c>
       <c r="R55" t="n">
-        <v>6524857</v>
+        <v>6524893</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6460,11 +6465,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6494,7 +6494,7 @@
         <v>127981257</v>
       </c>
       <c r="B56" t="n">
-        <v>79115</v>
+        <v>79118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>127980871</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985560</v>
+        <v>127985115</v>
       </c>
       <c r="B61" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7040,21 +7040,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519553</v>
+        <v>519590</v>
       </c>
       <c r="R61" t="n">
-        <v>6524821</v>
+        <v>6524878</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127985115</v>
+        <v>127985560</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,21 +7147,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519590</v>
+        <v>519553</v>
       </c>
       <c r="R62" t="n">
-        <v>6524878</v>
+        <v>6524821</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>8439</v>
+        <v>96080</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,32 +7360,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7393,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R64" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7456,10 +7455,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B65" t="n">
-        <v>96072</v>
+        <v>8439</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,31 +7466,32 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R65" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127987178</v>
+        <v>127948726</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +4034,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519677</v>
+        <v>520092</v>
       </c>
       <c r="R33" t="n">
-        <v>6524696</v>
+        <v>6524842</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,7 +4111,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4130,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948726</v>
+        <v>127948430</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,21 +4140,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520092</v>
+        <v>520103</v>
       </c>
       <c r="R34" t="n">
-        <v>6524842</v>
+        <v>6524835</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4236,7 +4235,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127948430</v>
+        <v>127987178</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4280,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520103</v>
+        <v>519677</v>
       </c>
       <c r="R35" t="n">
-        <v>6524835</v>
+        <v>6524696</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4324,6 +4323,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127981257</v>
+        <v>127984457</v>
       </c>
       <c r="B56" t="n">
-        <v>79118</v>
+        <v>6272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,30 +6502,32 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6450</v>
+        <v>105336</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6533,10 +6535,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519957</v>
+        <v>519670</v>
       </c>
       <c r="R56" t="n">
-        <v>6524845</v>
+        <v>6524879</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6596,10 +6598,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127984457</v>
+        <v>127979259</v>
       </c>
       <c r="B57" t="n">
-        <v>6272</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,32 +6609,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6640,10 +6642,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519670</v>
+        <v>520006</v>
       </c>
       <c r="R57" t="n">
-        <v>6524879</v>
+        <v>6524801</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6684,7 +6686,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6703,7 +6704,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127979259</v>
+        <v>127984642</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6747,10 +6748,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520006</v>
+        <v>519633</v>
       </c>
       <c r="R58" t="n">
-        <v>6524801</v>
+        <v>6524919</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6791,6 +6792,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6809,10 +6811,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127984642</v>
+        <v>127981257</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6820,32 +6822,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6450</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519633</v>
+        <v>519957</v>
       </c>
       <c r="R59" t="n">
-        <v>6524919</v>
+        <v>6524845</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127986450</v>
+        <v>127948538</v>
       </c>
       <c r="B3" t="n">
-        <v>92678</v>
+        <v>79702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,27 +799,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519639</v>
+        <v>520098</v>
       </c>
       <c r="R3" t="n">
-        <v>6524788</v>
+        <v>6524835</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +895,7 @@
         <v>127983115</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127981516</v>
+        <v>127986585</v>
       </c>
       <c r="B5" t="n">
         <v>8450</v>
@@ -1046,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519856</v>
+        <v>519663</v>
       </c>
       <c r="R5" t="n">
-        <v>6524816</v>
+        <v>6524783</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127986585</v>
+        <v>127988398</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519663</v>
+        <v>519897</v>
       </c>
       <c r="R6" t="n">
-        <v>6524783</v>
+        <v>6524632</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127988398</v>
+        <v>127981516</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1260,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519897</v>
+        <v>519856</v>
       </c>
       <c r="R7" t="n">
-        <v>6524632</v>
+        <v>6524816</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1429,41 +1428,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127948538</v>
+        <v>127979097</v>
       </c>
       <c r="B9" t="n">
-        <v>79650</v>
+        <v>40084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>214803</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1471,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520098</v>
+        <v>520012</v>
       </c>
       <c r="R9" t="n">
-        <v>6524835</v>
+        <v>6524809</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1507,6 +1508,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,43 +1539,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127979097</v>
+        <v>127986450</v>
       </c>
       <c r="B10" t="n">
-        <v>40076</v>
+        <v>92770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>214803</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520012</v>
+        <v>519639</v>
       </c>
       <c r="R10" t="n">
-        <v>6524809</v>
+        <v>6524788</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,17 +1619,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>127984949</v>
       </c>
       <c r="B11" t="n">
-        <v>40076</v>
+        <v>40084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127988511</v>
+        <v>127948647</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519885</v>
+        <v>520100</v>
       </c>
       <c r="R12" t="n">
-        <v>6524640</v>
+        <v>6524842</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1838,13 +1838,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127981103</v>
+        <v>127949128</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519953</v>
+        <v>520070</v>
       </c>
       <c r="R13" t="n">
-        <v>6524860</v>
+        <v>6524851</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1943,6 +1947,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127948647</v>
+        <v>127981103</v>
       </c>
       <c r="B14" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1989,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520100</v>
+        <v>519953</v>
       </c>
       <c r="R14" t="n">
-        <v>6524842</v>
+        <v>6524860</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2049,11 +2058,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127949128</v>
+        <v>127988511</v>
       </c>
       <c r="B15" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,21 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520070</v>
+        <v>519885</v>
       </c>
       <c r="R15" t="n">
-        <v>6524851</v>
+        <v>6524640</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2162,17 +2166,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127979875</v>
+        <v>127985911</v>
       </c>
       <c r="B16" t="n">
-        <v>96080</v>
+        <v>40084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,31 +2202,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519924</v>
+        <v>519623</v>
       </c>
       <c r="R16" t="n">
-        <v>6524793</v>
+        <v>6524788</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2249,7 +2250,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2259,7 +2260,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2272,12 +2273,18 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127985911</v>
+        <v>127978774</v>
       </c>
       <c r="B17" t="n">
-        <v>40076</v>
+        <v>40084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519623</v>
+        <v>520015</v>
       </c>
       <c r="R17" t="n">
-        <v>6524788</v>
+        <v>6524853</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2355,7 +2362,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2365,7 +2372,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2389,7 +2396,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127978774</v>
+        <v>127979875</v>
       </c>
       <c r="B18" t="n">
-        <v>40076</v>
+        <v>96173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,32 +2425,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520015</v>
+        <v>519924</v>
       </c>
       <c r="R18" t="n">
-        <v>6524853</v>
+        <v>6524793</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2488,11 +2493,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,41 +2626,44 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127982418</v>
+        <v>127983089</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2670,13 +2673,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519808</v>
+        <v>519891</v>
       </c>
       <c r="R20" t="n">
-        <v>6524877</v>
+        <v>6524716</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,7 +2717,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,44 +2735,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127983089</v>
+        <v>127982168</v>
       </c>
       <c r="B21" t="n">
-        <v>57833</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2780,13 +2779,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519891</v>
+        <v>519819</v>
       </c>
       <c r="R21" t="n">
-        <v>6524716</v>
+        <v>6524878</v>
       </c>
       <c r="S21" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2824,6 +2823,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127982168</v>
+        <v>127982418</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519819</v>
+        <v>519808</v>
       </c>
       <c r="R22" t="n">
-        <v>6524878</v>
+        <v>6524877</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2952,7 +2952,7 @@
         <v>127985397</v>
       </c>
       <c r="B23" t="n">
-        <v>40076</v>
+        <v>40084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>127948923</v>
       </c>
       <c r="B24" t="n">
-        <v>40076</v>
+        <v>40084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127984194</v>
+        <v>127988256</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>96173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,32 +3608,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3641,10 +3640,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519680</v>
+        <v>519889</v>
       </c>
       <c r="R29" t="n">
-        <v>6524874</v>
+        <v>6524614</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3704,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127988256</v>
+        <v>127984194</v>
       </c>
       <c r="B30" t="n">
-        <v>96080</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3715,31 +3714,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519889</v>
+        <v>519680</v>
       </c>
       <c r="R30" t="n">
-        <v>6524614</v>
+        <v>6524874</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4342,41 +4342,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127986395</v>
+        <v>127950052</v>
       </c>
       <c r="B36" t="n">
-        <v>92642</v>
+        <v>40084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>214803</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519639</v>
+        <v>520044</v>
       </c>
       <c r="R36" t="n">
-        <v>6524788</v>
+        <v>6524903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4422,13 +4424,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,43 +4453,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127987059</v>
+        <v>127986395</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>92734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4491,10 +4495,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519688</v>
+        <v>519639</v>
       </c>
       <c r="R37" t="n">
-        <v>6524694</v>
+        <v>6524788</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4554,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127950052</v>
+        <v>127987059</v>
       </c>
       <c r="B38" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,21 +4569,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520044</v>
+        <v>519688</v>
       </c>
       <c r="R38" t="n">
-        <v>6524903</v>
+        <v>6524694</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,17 +4640,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B42" t="n">
-        <v>96080</v>
+        <v>40084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,31 +4994,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R42" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5064,13 +5065,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127981664</v>
+        <v>127983788</v>
       </c>
       <c r="B43" t="n">
-        <v>4773</v>
+        <v>96173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5100,32 +5105,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5133,10 +5137,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519843</v>
+        <v>519717</v>
       </c>
       <c r="R43" t="n">
-        <v>6524831</v>
+        <v>6524808</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5196,10 +5200,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127980473</v>
+        <v>127981664</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>4773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,21 +5211,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5240,7 +5244,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519985</v>
+        <v>519843</v>
       </c>
       <c r="R44" t="n">
         <v>6524831</v>
@@ -5284,6 +5288,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5409,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127979704</v>
+        <v>127980473</v>
       </c>
       <c r="B46" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5420,21 +5425,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5453,10 +5458,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519952</v>
+        <v>519985</v>
       </c>
       <c r="R46" t="n">
-        <v>6524773</v>
+        <v>6524831</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5489,11 +5494,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5520,41 +5520,43 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127984700</v>
+        <v>127980279</v>
       </c>
       <c r="B47" t="n">
-        <v>81007</v>
+        <v>40084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>214803</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5562,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519633</v>
+        <v>519975</v>
       </c>
       <c r="R47" t="n">
-        <v>6524919</v>
+        <v>6524804</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5600,13 +5602,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5625,43 +5631,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127985707</v>
+        <v>127984700</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>81068</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5669,10 +5673,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519596</v>
+        <v>519633</v>
       </c>
       <c r="R48" t="n">
-        <v>6524811</v>
+        <v>6524919</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5684,7 +5688,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5694,7 +5698,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5732,10 +5736,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B49" t="n">
-        <v>40076</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5743,21 +5747,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5776,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R49" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5791,7 +5795,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5801,7 +5805,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5814,17 +5818,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127949357</v>
+        <v>127950593</v>
       </c>
       <c r="B50" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520055</v>
+        <v>519991</v>
       </c>
       <c r="R50" t="n">
-        <v>6524858</v>
+        <v>6524893</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,11 +5923,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127949218</v>
+        <v>127979471</v>
       </c>
       <c r="B51" t="n">
-        <v>40076</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520067</v>
+        <v>519986</v>
       </c>
       <c r="R51" t="n">
-        <v>6524857</v>
+        <v>6524777</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6034,11 +6029,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6065,7 +6055,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127987902</v>
+        <v>127983540</v>
       </c>
       <c r="B52" t="n">
         <v>8450</v>
@@ -6109,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519738</v>
+        <v>519733</v>
       </c>
       <c r="R52" t="n">
-        <v>6524605</v>
+        <v>6524792</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6172,10 +6162,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127979471</v>
+        <v>127987902</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,21 +6173,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6216,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519986</v>
+        <v>519738</v>
       </c>
       <c r="R53" t="n">
-        <v>6524777</v>
+        <v>6524605</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6260,6 +6250,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6278,10 +6269,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127983540</v>
+        <v>127949357</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,21 +6280,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6322,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519733</v>
+        <v>520055</v>
       </c>
       <c r="R54" t="n">
-        <v>6524792</v>
+        <v>6524858</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6360,13 +6351,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6385,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127950593</v>
+        <v>127949218</v>
       </c>
       <c r="B55" t="n">
-        <v>8439</v>
+        <v>40084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6391,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6429,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519991</v>
+        <v>520067</v>
       </c>
       <c r="R55" t="n">
-        <v>6524893</v>
+        <v>6524857</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6465,6 +6460,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127984457</v>
+        <v>127981257</v>
       </c>
       <c r="B56" t="n">
-        <v>6272</v>
+        <v>79169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,32 +6502,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105336</v>
+        <v>6450</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6535,10 +6533,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519670</v>
+        <v>519957</v>
       </c>
       <c r="R56" t="n">
-        <v>6524879</v>
+        <v>6524845</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6811,10 +6809,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127981257</v>
+        <v>127984457</v>
       </c>
       <c r="B59" t="n">
-        <v>79118</v>
+        <v>6272</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6822,30 +6820,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6450</v>
+        <v>105336</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519957</v>
+        <v>519670</v>
       </c>
       <c r="R59" t="n">
-        <v>6524845</v>
+        <v>6524879</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6916,45 +6916,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127980871</v>
+        <v>127985560</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6962,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519964</v>
+        <v>519553</v>
       </c>
       <c r="R60" t="n">
-        <v>6524859</v>
+        <v>6524821</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6977,7 +6975,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6987,7 +6985,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -7000,17 +6998,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>på tall</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7136,10 +7130,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127985560</v>
+        <v>127980055</v>
       </c>
       <c r="B62" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,21 +7141,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7180,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519553</v>
+        <v>519943</v>
       </c>
       <c r="R62" t="n">
-        <v>6524821</v>
+        <v>6524799</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7195,7 +7189,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7205,7 +7199,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7224,7 +7218,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7243,43 +7236,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980055</v>
+        <v>127980871</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7287,10 +7282,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519943</v>
+        <v>519964</v>
       </c>
       <c r="R63" t="n">
-        <v>6524799</v>
+        <v>6524859</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7323,6 +7318,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7352,7 +7352,7 @@
         <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127983115</v>
+        <v>127986450</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>92770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,35 +903,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519891</v>
+        <v>519639</v>
       </c>
       <c r="R4" t="n">
-        <v>6524716</v>
+        <v>6524788</v>
       </c>
       <c r="S4" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986585</v>
+        <v>127979097</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519663</v>
+        <v>520012</v>
       </c>
       <c r="R5" t="n">
-        <v>6524783</v>
+        <v>6524809</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,13 +1079,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127988398</v>
+        <v>127986585</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519897</v>
+        <v>519663</v>
       </c>
       <c r="R6" t="n">
-        <v>6524632</v>
+        <v>6524783</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127981516</v>
+        <v>127988398</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519856</v>
+        <v>519897</v>
       </c>
       <c r="R7" t="n">
-        <v>6524816</v>
+        <v>6524632</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127980622</v>
+        <v>127981516</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519968</v>
+        <v>519856</v>
       </c>
       <c r="R8" t="n">
-        <v>6524851</v>
+        <v>6524816</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,6 +1410,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1428,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127979097</v>
+        <v>127980622</v>
       </c>
       <c r="B9" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1439,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520012</v>
+        <v>519968</v>
       </c>
       <c r="R9" t="n">
-        <v>6524809</v>
+        <v>6524851</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1508,11 +1509,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127986450</v>
+        <v>127983115</v>
       </c>
       <c r="B10" t="n">
-        <v>92770</v>
+        <v>57682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,30 +1546,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,13 +1582,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519639</v>
+        <v>519891</v>
       </c>
       <c r="R10" t="n">
-        <v>6524788</v>
+        <v>6524716</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1625,7 +1626,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2626,44 +2626,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127983089</v>
+        <v>127982168</v>
       </c>
       <c r="B20" t="n">
-        <v>57845</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2673,13 +2670,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519891</v>
+        <v>519819</v>
       </c>
       <c r="R20" t="n">
-        <v>6524716</v>
+        <v>6524878</v>
       </c>
       <c r="S20" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2717,6 +2714,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2735,7 +2733,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982168</v>
+        <v>127982418</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2779,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519819</v>
+        <v>519808</v>
       </c>
       <c r="R21" t="n">
-        <v>6524878</v>
+        <v>6524877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2842,41 +2840,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127982418</v>
+        <v>127983089</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2886,13 +2887,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519808</v>
+        <v>519891</v>
       </c>
       <c r="R22" t="n">
-        <v>6524877</v>
+        <v>6524716</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2931,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127982588</v>
+        <v>127949748</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519798</v>
+        <v>520046</v>
       </c>
       <c r="R25" t="n">
-        <v>6524851</v>
+        <v>6524882</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,7 +3260,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3279,7 +3278,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127950272</v>
+        <v>127982588</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3323,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520031</v>
+        <v>519798</v>
       </c>
       <c r="R26" t="n">
-        <v>6524880</v>
+        <v>6524851</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3367,6 +3366,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950402</v>
+        <v>127950272</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520020</v>
+        <v>520031</v>
       </c>
       <c r="R27" t="n">
-        <v>6524923</v>
+        <v>6524880</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127949748</v>
+        <v>127950402</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520046</v>
+        <v>520020</v>
       </c>
       <c r="R28" t="n">
-        <v>6524882</v>
+        <v>6524923</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127948726</v>
+        <v>127987178</v>
       </c>
       <c r="B33" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +4034,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520092</v>
+        <v>519677</v>
       </c>
       <c r="R33" t="n">
-        <v>6524842</v>
+        <v>6524696</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,6 +4111,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4130,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948430</v>
+        <v>127948726</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,21 +4141,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4173,10 +4174,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520103</v>
+        <v>520092</v>
       </c>
       <c r="R34" t="n">
-        <v>6524835</v>
+        <v>6524842</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,7 +4236,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127987178</v>
+        <v>127948430</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4279,10 +4280,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519677</v>
+        <v>520103</v>
       </c>
       <c r="R35" t="n">
-        <v>6524696</v>
+        <v>6524835</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4323,7 +4324,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4342,43 +4342,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>40084</v>
+        <v>92734</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R36" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,17 +4422,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,41 +4447,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127986395</v>
+        <v>127987059</v>
       </c>
       <c r="B37" t="n">
-        <v>92734</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4495,10 +4491,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519639</v>
+        <v>519688</v>
       </c>
       <c r="R37" t="n">
-        <v>6524788</v>
+        <v>6524694</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4558,10 +4554,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127987059</v>
+        <v>127950052</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4569,21 +4565,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4602,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519688</v>
+        <v>520044</v>
       </c>
       <c r="R38" t="n">
-        <v>6524694</v>
+        <v>6524903</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4640,13 +4636,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127979704</v>
+        <v>127983788</v>
       </c>
       <c r="B42" t="n">
-        <v>40084</v>
+        <v>96173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,32 +4994,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519952</v>
+        <v>519717</v>
       </c>
       <c r="R42" t="n">
-        <v>6524773</v>
+        <v>6524808</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5065,17 +5064,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5094,10 +5089,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127983788</v>
+        <v>127981664</v>
       </c>
       <c r="B43" t="n">
-        <v>96173</v>
+        <v>4773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5105,31 +5100,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5137,10 +5133,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519717</v>
+        <v>519843</v>
       </c>
       <c r="R43" t="n">
-        <v>6524808</v>
+        <v>6524831</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5200,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127981664</v>
+        <v>127979704</v>
       </c>
       <c r="B44" t="n">
-        <v>4773</v>
+        <v>40084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,21 +5207,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100299</v>
+        <v>214803</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5244,10 +5240,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519843</v>
+        <v>519952</v>
       </c>
       <c r="R44" t="n">
-        <v>6524831</v>
+        <v>6524773</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5282,13 +5278,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B47" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,21 +5531,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R47" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5602,17 +5602,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5736,10 +5732,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5747,21 +5743,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5780,10 +5776,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R49" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5795,7 +5791,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5805,7 +5801,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5818,13 +5814,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127950593</v>
+        <v>127949357</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>40084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519991</v>
+        <v>520055</v>
       </c>
       <c r="R50" t="n">
-        <v>6524893</v>
+        <v>6524858</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,6 +5923,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,10 +5954,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127979471</v>
+        <v>127949218</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>40084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5965,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519986</v>
+        <v>520067</v>
       </c>
       <c r="R51" t="n">
-        <v>6524777</v>
+        <v>6524857</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6029,6 +6034,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6055,10 +6065,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127983540</v>
+        <v>127950593</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,21 +6076,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6109,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519733</v>
+        <v>519991</v>
       </c>
       <c r="R52" t="n">
-        <v>6524792</v>
+        <v>6524893</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6143,7 +6153,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6162,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127987902</v>
+        <v>127979471</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6173,21 +6182,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6215,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519738</v>
+        <v>519986</v>
       </c>
       <c r="R53" t="n">
-        <v>6524605</v>
+        <v>6524777</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6250,7 +6259,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6269,10 +6277,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127949357</v>
+        <v>127987902</v>
       </c>
       <c r="B54" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6280,21 +6288,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6313,10 +6321,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520055</v>
+        <v>519738</v>
       </c>
       <c r="R54" t="n">
-        <v>6524858</v>
+        <v>6524605</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6351,17 +6359,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6380,10 +6384,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127949218</v>
+        <v>127983540</v>
       </c>
       <c r="B55" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,21 +6395,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6428,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520067</v>
+        <v>519733</v>
       </c>
       <c r="R55" t="n">
-        <v>6524857</v>
+        <v>6524792</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6462,17 +6466,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127981257</v>
+        <v>127984457</v>
       </c>
       <c r="B56" t="n">
-        <v>79169</v>
+        <v>6272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,30 +6502,32 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6450</v>
+        <v>105336</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6533,10 +6535,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519957</v>
+        <v>519670</v>
       </c>
       <c r="R56" t="n">
-        <v>6524845</v>
+        <v>6524879</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6809,10 +6811,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127984457</v>
+        <v>127981257</v>
       </c>
       <c r="B59" t="n">
-        <v>6272</v>
+        <v>79169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6820,32 +6822,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105336</v>
+        <v>6450</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519670</v>
+        <v>519957</v>
       </c>
       <c r="R59" t="n">
-        <v>6524879</v>
+        <v>6524845</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B64" t="n">
-        <v>96173</v>
+        <v>8439</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,31 +7360,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7392,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R64" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7455,10 +7456,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B65" t="n">
-        <v>8439</v>
+        <v>96173</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7466,32 +7467,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R65" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,41 +788,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127948538</v>
+        <v>127986585</v>
       </c>
       <c r="B3" t="n">
-        <v>79702</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520098</v>
+        <v>519663</v>
       </c>
       <c r="R3" t="n">
-        <v>6524835</v>
+        <v>6524783</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,6 +876,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,41 +895,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127986450</v>
+        <v>127988398</v>
       </c>
       <c r="B4" t="n">
-        <v>92770</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519639</v>
+        <v>519897</v>
       </c>
       <c r="R4" t="n">
-        <v>6524788</v>
+        <v>6524632</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127979097</v>
+        <v>127981516</v>
       </c>
       <c r="B5" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1008,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520012</v>
+        <v>519856</v>
       </c>
       <c r="R5" t="n">
-        <v>6524809</v>
+        <v>6524816</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,17 +1084,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127986585</v>
+        <v>127980622</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519663</v>
+        <v>519968</v>
       </c>
       <c r="R6" t="n">
-        <v>6524783</v>
+        <v>6524851</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,43 +1215,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127988398</v>
+        <v>127948538</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79702</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519897</v>
+        <v>520098</v>
       </c>
       <c r="R7" t="n">
-        <v>6524632</v>
+        <v>6524835</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1303,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,43 +1319,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127981516</v>
+        <v>127986450</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>92770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1366,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519856</v>
+        <v>519639</v>
       </c>
       <c r="R8" t="n">
-        <v>6524816</v>
+        <v>6524788</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,41 +1424,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127980622</v>
+        <v>127983115</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1473,13 +1471,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519968</v>
+        <v>519891</v>
       </c>
       <c r="R9" t="n">
-        <v>6524851</v>
+        <v>6524716</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,44 +1533,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127983115</v>
+        <v>127979097</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>40084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>214803</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1582,13 +1577,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519891</v>
+        <v>520012</v>
       </c>
       <c r="R10" t="n">
-        <v>6524716</v>
+        <v>6524809</v>
       </c>
       <c r="S10" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127948647</v>
+        <v>127981103</v>
       </c>
       <c r="B12" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520100</v>
+        <v>519953</v>
       </c>
       <c r="R12" t="n">
-        <v>6524842</v>
+        <v>6524860</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,11 +1836,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127949128</v>
+        <v>127988511</v>
       </c>
       <c r="B13" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520070</v>
+        <v>519885</v>
       </c>
       <c r="R13" t="n">
-        <v>6524851</v>
+        <v>6524640</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1949,17 +1944,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1978,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127981103</v>
+        <v>127948647</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519953</v>
+        <v>520100</v>
       </c>
       <c r="R14" t="n">
-        <v>6524860</v>
+        <v>6524842</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2058,6 +2049,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127988511</v>
+        <v>127949128</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519885</v>
+        <v>520070</v>
       </c>
       <c r="R15" t="n">
-        <v>6524640</v>
+        <v>6524851</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2166,13 +2162,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2626,41 +2626,44 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127982168</v>
+        <v>127983089</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>57845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2670,13 +2673,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519819</v>
+        <v>519891</v>
       </c>
       <c r="R20" t="n">
-        <v>6524878</v>
+        <v>6524716</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,7 +2717,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,7 +2735,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982418</v>
+        <v>127982168</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2777,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519808</v>
+        <v>519819</v>
       </c>
       <c r="R21" t="n">
-        <v>6524877</v>
+        <v>6524878</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2840,44 +2842,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127983089</v>
+        <v>127982418</v>
       </c>
       <c r="B22" t="n">
-        <v>57845</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2887,13 +2886,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519891</v>
+        <v>519808</v>
       </c>
       <c r="R22" t="n">
-        <v>6524716</v>
+        <v>6524877</v>
       </c>
       <c r="S22" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2931,6 +2930,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127949748</v>
+        <v>127982588</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520046</v>
+        <v>519798</v>
       </c>
       <c r="R25" t="n">
-        <v>6524882</v>
+        <v>6524851</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,6 +3260,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3278,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127982588</v>
+        <v>127950272</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3322,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519798</v>
+        <v>520031</v>
       </c>
       <c r="R26" t="n">
-        <v>6524851</v>
+        <v>6524880</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3366,7 +3367,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950272</v>
+        <v>127950402</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520031</v>
+        <v>520020</v>
       </c>
       <c r="R27" t="n">
-        <v>6524880</v>
+        <v>6524923</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127950402</v>
+        <v>127949748</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520020</v>
+        <v>520046</v>
       </c>
       <c r="R28" t="n">
-        <v>6524923</v>
+        <v>6524882</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R31" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,6 +3898,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3916,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3960,10 +3961,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R32" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4004,7 +4005,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4342,41 +4342,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127986395</v>
+        <v>127950052</v>
       </c>
       <c r="B36" t="n">
-        <v>92734</v>
+        <v>40084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>214803</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519639</v>
+        <v>520044</v>
       </c>
       <c r="R36" t="n">
-        <v>6524788</v>
+        <v>6524903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4422,13 +4424,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4554,43 +4560,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B38" t="n">
-        <v>40084</v>
+        <v>92734</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4598,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R38" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,17 +4640,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B42" t="n">
-        <v>96173</v>
+        <v>40084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,31 +4994,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R42" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5064,13 +5065,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127981664</v>
+        <v>127982266</v>
       </c>
       <c r="B43" t="n">
-        <v>4773</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5100,21 +5105,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5133,10 +5138,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519843</v>
+        <v>519814</v>
       </c>
       <c r="R43" t="n">
-        <v>6524831</v>
+        <v>6524877</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5196,10 +5201,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127979704</v>
+        <v>127980473</v>
       </c>
       <c r="B44" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,21 +5212,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5240,10 +5245,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519952</v>
+        <v>519985</v>
       </c>
       <c r="R44" t="n">
-        <v>6524773</v>
+        <v>6524831</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5276,11 +5281,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127982266</v>
+        <v>127981664</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>4773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,21 +5318,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519814</v>
+        <v>519843</v>
       </c>
       <c r="R45" t="n">
-        <v>6524877</v>
+        <v>6524831</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5414,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127980473</v>
+        <v>127983788</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>96173</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5425,32 +5425,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5458,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519985</v>
+        <v>519717</v>
       </c>
       <c r="R46" t="n">
-        <v>6524831</v>
+        <v>6524808</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5502,6 +5501,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5531,21 +5531,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R47" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5602,13 +5602,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5732,10 +5736,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127980279</v>
+        <v>127985707</v>
       </c>
       <c r="B49" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5743,21 +5747,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5776,10 +5780,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519975</v>
+        <v>519596</v>
       </c>
       <c r="R49" t="n">
-        <v>6524804</v>
+        <v>6524811</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5791,7 +5795,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5801,7 +5805,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5814,17 +5818,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127949357</v>
+        <v>127950593</v>
       </c>
       <c r="B50" t="n">
-        <v>40084</v>
+        <v>8439</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520055</v>
+        <v>519991</v>
       </c>
       <c r="R50" t="n">
-        <v>6524858</v>
+        <v>6524893</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,11 +5923,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,10 +5949,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127949218</v>
+        <v>127979471</v>
       </c>
       <c r="B51" t="n">
-        <v>40084</v>
+        <v>8439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,21 +5960,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520067</v>
+        <v>519986</v>
       </c>
       <c r="R51" t="n">
-        <v>6524857</v>
+        <v>6524777</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6034,11 +6029,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6065,10 +6055,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127950593</v>
+        <v>127987902</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6076,21 +6066,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6109,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519991</v>
+        <v>519738</v>
       </c>
       <c r="R52" t="n">
-        <v>6524893</v>
+        <v>6524605</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6153,6 +6143,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6162,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127979471</v>
+        <v>127983540</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,21 +6173,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6215,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519986</v>
+        <v>519733</v>
       </c>
       <c r="R53" t="n">
-        <v>6524777</v>
+        <v>6524792</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6259,6 +6250,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6277,10 +6269,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127987902</v>
+        <v>127949357</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,21 +6280,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6321,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519738</v>
+        <v>520055</v>
       </c>
       <c r="R54" t="n">
-        <v>6524605</v>
+        <v>6524858</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6359,13 +6351,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6384,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127983540</v>
+        <v>127949218</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6395,21 +6391,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6428,10 +6424,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519733</v>
+        <v>520067</v>
       </c>
       <c r="R55" t="n">
-        <v>6524792</v>
+        <v>6524857</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6466,13 +6462,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6916,43 +6916,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127985560</v>
+        <v>127980871</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6960,10 +6962,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519553</v>
+        <v>519964</v>
       </c>
       <c r="R60" t="n">
-        <v>6524821</v>
+        <v>6524859</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6975,7 +6977,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6985,7 +6987,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -6998,13 +7000,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>på tall</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7023,10 +7029,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985115</v>
+        <v>127985560</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7034,21 +7040,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7073,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519590</v>
+        <v>519553</v>
       </c>
       <c r="R61" t="n">
-        <v>6524878</v>
+        <v>6524821</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7130,7 +7136,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127980055</v>
+        <v>127985115</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7174,10 +7180,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519943</v>
+        <v>519590</v>
       </c>
       <c r="R62" t="n">
-        <v>6524799</v>
+        <v>6524878</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7189,7 +7195,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7199,7 +7205,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7218,6 +7224,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7236,45 +7243,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980871</v>
+        <v>127980055</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7282,10 +7287,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519964</v>
+        <v>519943</v>
       </c>
       <c r="R63" t="n">
-        <v>6524859</v>
+        <v>6524799</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7318,11 +7323,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>8439</v>
+        <v>96173</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,32 +7360,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7393,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R64" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7456,10 +7455,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B65" t="n">
-        <v>96173</v>
+        <v>8439</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,31 +7466,32 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R65" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,43 +788,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127986585</v>
+        <v>127948538</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>79702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519663</v>
+        <v>520098</v>
       </c>
       <c r="R3" t="n">
-        <v>6524783</v>
+        <v>6524835</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127988398</v>
+        <v>127986585</v>
       </c>
       <c r="B4" t="n">
         <v>8450</v>
@@ -939,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519897</v>
+        <v>519663</v>
       </c>
       <c r="R4" t="n">
-        <v>6524632</v>
+        <v>6524783</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127981516</v>
+        <v>127988398</v>
       </c>
       <c r="B5" t="n">
         <v>8450</v>
@@ -1046,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519856</v>
+        <v>519897</v>
       </c>
       <c r="R5" t="n">
-        <v>6524816</v>
+        <v>6524632</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127980622</v>
+        <v>127981516</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1153,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519968</v>
+        <v>519856</v>
       </c>
       <c r="R6" t="n">
-        <v>6524851</v>
+        <v>6524816</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1197,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,41 +1213,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127948538</v>
+        <v>127980622</v>
       </c>
       <c r="B7" t="n">
-        <v>79702</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520098</v>
+        <v>519968</v>
       </c>
       <c r="R7" t="n">
-        <v>6524835</v>
+        <v>6524851</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,41 +1319,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127986450</v>
+        <v>127979097</v>
       </c>
       <c r="B8" t="n">
-        <v>92770</v>
+        <v>40084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>214803</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519639</v>
+        <v>520012</v>
       </c>
       <c r="R8" t="n">
-        <v>6524788</v>
+        <v>6524809</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1399,13 +1401,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127983115</v>
+        <v>127986450</v>
       </c>
       <c r="B9" t="n">
-        <v>57682</v>
+        <v>92770</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,35 +1441,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1471,13 +1472,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519891</v>
+        <v>519639</v>
       </c>
       <c r="R9" t="n">
-        <v>6524716</v>
+        <v>6524788</v>
       </c>
       <c r="S9" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,6 +1516,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,41 +1535,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127979097</v>
+        <v>127983115</v>
       </c>
       <c r="B10" t="n">
-        <v>40084</v>
+        <v>57682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>214803</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1577,13 +1582,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520012</v>
+        <v>519891</v>
       </c>
       <c r="R10" t="n">
-        <v>6524809</v>
+        <v>6524716</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4342,43 +4342,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127950052</v>
+        <v>127986395</v>
       </c>
       <c r="B36" t="n">
-        <v>40084</v>
+        <v>92734</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214803</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,10 +4384,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520044</v>
+        <v>519639</v>
       </c>
       <c r="R36" t="n">
-        <v>6524903</v>
+        <v>6524788</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4424,17 +4422,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4560,41 +4554,43 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127986395</v>
+        <v>127950052</v>
       </c>
       <c r="B38" t="n">
-        <v>92734</v>
+        <v>40084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>214803</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4602,10 +4598,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519639</v>
+        <v>520044</v>
       </c>
       <c r="R38" t="n">
-        <v>6524788</v>
+        <v>6524903</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4640,13 +4636,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127978914</v>
+        <v>127988102</v>
       </c>
       <c r="B39" t="n">
-        <v>92742</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,30 +4676,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4707,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520021</v>
+        <v>519876</v>
       </c>
       <c r="R39" t="n">
-        <v>6524832</v>
+        <v>6524610</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4751,6 +4753,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4769,7 +4772,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4813,10 +4816,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R40" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4876,10 +4879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127986860</v>
+        <v>127978914</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>92742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,32 +4890,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4920,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519744</v>
+        <v>520021</v>
       </c>
       <c r="R41" t="n">
-        <v>6524735</v>
+        <v>6524832</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4964,7 +4965,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5520,43 +5520,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127980279</v>
+        <v>127984700</v>
       </c>
       <c r="B47" t="n">
-        <v>40084</v>
+        <v>81068</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>214803</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5564,10 +5562,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519975</v>
+        <v>519633</v>
       </c>
       <c r="R47" t="n">
-        <v>6524804</v>
+        <v>6524919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5602,17 +5600,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5631,41 +5625,43 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127984700</v>
+        <v>127985707</v>
       </c>
       <c r="B48" t="n">
-        <v>81068</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5673,10 +5669,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519633</v>
+        <v>519596</v>
       </c>
       <c r="R48" t="n">
-        <v>6524919</v>
+        <v>6524811</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5688,7 +5684,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5698,7 +5694,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5736,10 +5732,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127985707</v>
+        <v>127980279</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>40084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5747,21 +5743,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5780,10 +5776,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519596</v>
+        <v>519975</v>
       </c>
       <c r="R49" t="n">
-        <v>6524811</v>
+        <v>6524804</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5795,7 +5791,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5805,7 +5801,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5818,13 +5814,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127984457</v>
+        <v>127981257</v>
       </c>
       <c r="B56" t="n">
-        <v>6272</v>
+        <v>79169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,32 +6502,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105336</v>
+        <v>6450</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6535,10 +6533,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519670</v>
+        <v>519957</v>
       </c>
       <c r="R56" t="n">
-        <v>6524879</v>
+        <v>6524845</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6598,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127979259</v>
+        <v>127984457</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>6272</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6609,32 +6607,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6642,10 +6640,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520006</v>
+        <v>519670</v>
       </c>
       <c r="R57" t="n">
-        <v>6524801</v>
+        <v>6524879</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6686,6 +6684,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6704,7 +6703,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127984642</v>
+        <v>127979259</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6748,10 +6747,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519633</v>
+        <v>520006</v>
       </c>
       <c r="R58" t="n">
-        <v>6524919</v>
+        <v>6524801</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6792,7 +6791,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6811,10 +6809,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127981257</v>
+        <v>127984642</v>
       </c>
       <c r="B59" t="n">
-        <v>79169</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6822,30 +6820,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6450</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519957</v>
+        <v>519633</v>
       </c>
       <c r="R59" t="n">
-        <v>6524845</v>
+        <v>6524919</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B64" t="n">
-        <v>96173</v>
+        <v>8439</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,31 +7360,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7392,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R64" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7455,10 +7456,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B65" t="n">
-        <v>8439</v>
+        <v>96173</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7466,32 +7467,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R65" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>127948538</v>
       </c>
       <c r="B3" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,41 +892,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127986585</v>
+        <v>127983115</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -936,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519663</v>
+        <v>519891</v>
       </c>
       <c r="R4" t="n">
-        <v>6524783</v>
+        <v>6524716</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,43 +1001,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127988398</v>
+        <v>127986450</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>92782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519897</v>
+        <v>519639</v>
       </c>
       <c r="R5" t="n">
-        <v>6524632</v>
+        <v>6524788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127981516</v>
+        <v>127986585</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519856</v>
+        <v>519663</v>
       </c>
       <c r="R6" t="n">
-        <v>6524816</v>
+        <v>6524783</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127980622</v>
+        <v>127988398</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519968</v>
+        <v>519897</v>
       </c>
       <c r="R7" t="n">
-        <v>6524851</v>
+        <v>6524632</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1301,6 +1301,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127979097</v>
+        <v>127981516</v>
       </c>
       <c r="B8" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1330,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520012</v>
+        <v>519856</v>
       </c>
       <c r="R8" t="n">
-        <v>6524809</v>
+        <v>6524816</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1401,17 +1402,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1430,41 +1427,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127986450</v>
+        <v>127980622</v>
       </c>
       <c r="B9" t="n">
-        <v>92770</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1472,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519639</v>
+        <v>519968</v>
       </c>
       <c r="R9" t="n">
-        <v>6524788</v>
+        <v>6524851</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1516,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1535,44 +1533,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127983115</v>
+        <v>127979097</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>40086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>214803</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1582,13 +1577,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519891</v>
+        <v>520012</v>
       </c>
       <c r="R10" t="n">
-        <v>6524716</v>
+        <v>6524809</v>
       </c>
       <c r="S10" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,7 +1647,7 @@
         <v>127984949</v>
       </c>
       <c r="B11" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>127948647</v>
       </c>
       <c r="B14" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>127949128</v>
       </c>
       <c r="B15" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127985911</v>
+        <v>127979875</v>
       </c>
       <c r="B16" t="n">
-        <v>40084</v>
+        <v>96185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,32 +2202,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>214803</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2235,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519623</v>
+        <v>519924</v>
       </c>
       <c r="R16" t="n">
-        <v>6524788</v>
+        <v>6524793</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2250,7 +2249,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2260,7 +2259,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2273,18 +2272,12 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2303,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127978774</v>
+        <v>127985911</v>
       </c>
       <c r="B17" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520015</v>
+        <v>519623</v>
       </c>
       <c r="R17" t="n">
-        <v>6524853</v>
+        <v>6524788</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2362,7 +2355,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2372,7 +2365,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2396,6 +2389,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127979875</v>
+        <v>127978774</v>
       </c>
       <c r="B18" t="n">
-        <v>96173</v>
+        <v>40086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,31 +2419,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519924</v>
+        <v>520015</v>
       </c>
       <c r="R18" t="n">
-        <v>6524793</v>
+        <v>6524853</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2493,6 +2488,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,44 +2626,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127983089</v>
+        <v>127982168</v>
       </c>
       <c r="B20" t="n">
-        <v>57845</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2673,13 +2670,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519891</v>
+        <v>519819</v>
       </c>
       <c r="R20" t="n">
-        <v>6524716</v>
+        <v>6524878</v>
       </c>
       <c r="S20" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2717,6 +2714,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2735,7 +2733,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982168</v>
+        <v>127982418</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2779,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519819</v>
+        <v>519808</v>
       </c>
       <c r="R21" t="n">
-        <v>6524878</v>
+        <v>6524877</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2842,41 +2840,44 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127982418</v>
+        <v>127983089</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2886,13 +2887,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519808</v>
+        <v>519891</v>
       </c>
       <c r="R22" t="n">
-        <v>6524877</v>
+        <v>6524716</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2930,7 +2931,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>127985397</v>
       </c>
       <c r="B23" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>127948923</v>
       </c>
       <c r="B24" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127982588</v>
+        <v>127949748</v>
       </c>
       <c r="B25" t="n">
         <v>8450</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519798</v>
+        <v>520046</v>
       </c>
       <c r="R25" t="n">
-        <v>6524851</v>
+        <v>6524882</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3260,7 +3260,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3279,7 +3278,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127950272</v>
+        <v>127982588</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3323,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520031</v>
+        <v>519798</v>
       </c>
       <c r="R26" t="n">
-        <v>6524880</v>
+        <v>6524851</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3367,6 +3366,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950402</v>
+        <v>127950272</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520020</v>
+        <v>520031</v>
       </c>
       <c r="R27" t="n">
-        <v>6524923</v>
+        <v>6524880</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127949748</v>
+        <v>127950402</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520046</v>
+        <v>520020</v>
       </c>
       <c r="R28" t="n">
-        <v>6524882</v>
+        <v>6524923</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3600,7 +3600,7 @@
         <v>127988256</v>
       </c>
       <c r="B29" t="n">
-        <v>96173</v>
+        <v>96185</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127984020</v>
+        <v>127948850</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519675</v>
+        <v>520085</v>
       </c>
       <c r="R31" t="n">
-        <v>6524829</v>
+        <v>6524846</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,7 +3898,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3917,7 +3916,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127948850</v>
+        <v>127984020</v>
       </c>
       <c r="B32" t="n">
         <v>8450</v>
@@ -3961,10 +3960,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520085</v>
+        <v>519675</v>
       </c>
       <c r="R32" t="n">
-        <v>6524846</v>
+        <v>6524829</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4005,6 +4004,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127987178</v>
+        <v>127948726</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +4034,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519677</v>
+        <v>520092</v>
       </c>
       <c r="R33" t="n">
-        <v>6524696</v>
+        <v>6524842</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,7 +4111,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4130,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948726</v>
+        <v>127948430</v>
       </c>
       <c r="B34" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,21 +4140,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4174,10 +4173,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520092</v>
+        <v>520103</v>
       </c>
       <c r="R34" t="n">
-        <v>6524842</v>
+        <v>6524835</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4236,7 +4235,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127948430</v>
+        <v>127987178</v>
       </c>
       <c r="B35" t="n">
         <v>8450</v>
@@ -4280,10 +4279,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520103</v>
+        <v>519677</v>
       </c>
       <c r="R35" t="n">
-        <v>6524835</v>
+        <v>6524696</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4324,6 +4323,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4342,41 +4342,43 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127986395</v>
+        <v>127950052</v>
       </c>
       <c r="B36" t="n">
-        <v>92734</v>
+        <v>40086</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>214803</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4384,10 +4386,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519639</v>
+        <v>520044</v>
       </c>
       <c r="R36" t="n">
-        <v>6524788</v>
+        <v>6524903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4422,13 +4424,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,43 +4453,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127987059</v>
+        <v>127986395</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>92746</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4491,10 +4495,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519688</v>
+        <v>519639</v>
       </c>
       <c r="R37" t="n">
-        <v>6524694</v>
+        <v>6524788</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4554,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127950052</v>
+        <v>127987059</v>
       </c>
       <c r="B38" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,21 +4569,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4598,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520044</v>
+        <v>519688</v>
       </c>
       <c r="R38" t="n">
-        <v>6524903</v>
+        <v>6524694</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4636,17 +4640,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127988102</v>
+        <v>127978914</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>92754</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,32 +4676,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4709,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519876</v>
+        <v>520021</v>
       </c>
       <c r="R39" t="n">
-        <v>6524610</v>
+        <v>6524832</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4753,7 +4751,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4772,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127986860</v>
+        <v>127988102</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4816,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519744</v>
+        <v>519876</v>
       </c>
       <c r="R40" t="n">
-        <v>6524735</v>
+        <v>6524610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4879,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127978914</v>
+        <v>127986860</v>
       </c>
       <c r="B41" t="n">
-        <v>92742</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,30 +4887,32 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4921,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520021</v>
+        <v>519744</v>
       </c>
       <c r="R41" t="n">
-        <v>6524832</v>
+        <v>6524735</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4965,6 +4964,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127979704</v>
+        <v>127982266</v>
       </c>
       <c r="B42" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519952</v>
+        <v>519814</v>
       </c>
       <c r="R42" t="n">
-        <v>6524773</v>
+        <v>6524877</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5065,17 +5065,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5094,7 +5090,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127982266</v>
+        <v>127980473</v>
       </c>
       <c r="B43" t="n">
         <v>8450</v>
@@ -5138,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519814</v>
+        <v>519985</v>
       </c>
       <c r="R43" t="n">
-        <v>6524877</v>
+        <v>6524831</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5182,7 +5178,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5201,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127980473</v>
+        <v>127983788</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>96185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,32 +5207,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5245,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519985</v>
+        <v>519717</v>
       </c>
       <c r="R44" t="n">
-        <v>6524831</v>
+        <v>6524808</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5289,6 +5283,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5409,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127983788</v>
+        <v>127979704</v>
       </c>
       <c r="B46" t="n">
-        <v>96173</v>
+        <v>40086</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5425,31 +5420,32 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5457,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519717</v>
+        <v>519952</v>
       </c>
       <c r="R46" t="n">
-        <v>6524808</v>
+        <v>6524773</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5495,13 +5491,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>127984700</v>
       </c>
       <c r="B47" t="n">
-        <v>81068</v>
+        <v>81072</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>127980279</v>
       </c>
       <c r="B49" t="n">
-        <v>40084</v>
+        <v>40086</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5843,10 +5843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127950593</v>
+        <v>127949357</v>
       </c>
       <c r="B50" t="n">
-        <v>8439</v>
+        <v>40086</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519991</v>
+        <v>520055</v>
       </c>
       <c r="R50" t="n">
-        <v>6524893</v>
+        <v>6524858</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,6 +5923,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5949,10 +5954,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127979471</v>
+        <v>127949218</v>
       </c>
       <c r="B51" t="n">
-        <v>8439</v>
+        <v>40086</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,21 +5965,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5993,10 +5998,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519986</v>
+        <v>520067</v>
       </c>
       <c r="R51" t="n">
-        <v>6524777</v>
+        <v>6524857</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6029,6 +6034,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6055,10 +6065,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127987902</v>
+        <v>127950593</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,21 +6076,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6109,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519738</v>
+        <v>519991</v>
       </c>
       <c r="R52" t="n">
-        <v>6524605</v>
+        <v>6524893</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6143,7 +6153,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6162,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127983540</v>
+        <v>127979471</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6173,21 +6182,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6215,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519733</v>
+        <v>519986</v>
       </c>
       <c r="R53" t="n">
-        <v>6524792</v>
+        <v>6524777</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6250,7 +6259,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6269,10 +6277,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127949357</v>
+        <v>127987902</v>
       </c>
       <c r="B54" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6280,21 +6288,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6313,10 +6321,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520055</v>
+        <v>519738</v>
       </c>
       <c r="R54" t="n">
-        <v>6524858</v>
+        <v>6524605</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6351,17 +6359,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6380,10 +6384,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127949218</v>
+        <v>127983540</v>
       </c>
       <c r="B55" t="n">
-        <v>40084</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6391,21 +6395,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6424,10 +6428,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520067</v>
+        <v>519733</v>
       </c>
       <c r="R55" t="n">
-        <v>6524857</v>
+        <v>6524792</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6462,17 +6466,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127981257</v>
+        <v>127984457</v>
       </c>
       <c r="B56" t="n">
-        <v>79169</v>
+        <v>6272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,30 +6502,32 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6450</v>
+        <v>105336</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6533,10 +6535,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519957</v>
+        <v>519670</v>
       </c>
       <c r="R56" t="n">
-        <v>6524845</v>
+        <v>6524879</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6596,10 +6598,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127984457</v>
+        <v>127979259</v>
       </c>
       <c r="B57" t="n">
-        <v>6272</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,32 +6609,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6640,10 +6642,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519670</v>
+        <v>520006</v>
       </c>
       <c r="R57" t="n">
-        <v>6524879</v>
+        <v>6524801</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6684,7 +6686,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6703,7 +6704,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127979259</v>
+        <v>127984642</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6747,10 +6748,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520006</v>
+        <v>519633</v>
       </c>
       <c r="R58" t="n">
-        <v>6524801</v>
+        <v>6524919</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6791,6 +6792,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6809,10 +6811,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127984642</v>
+        <v>127981257</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79173</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6820,32 +6822,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6450</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519633</v>
+        <v>519957</v>
       </c>
       <c r="R59" t="n">
-        <v>6524919</v>
+        <v>6524845</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6916,45 +6916,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127980871</v>
+        <v>127985560</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6962,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519964</v>
+        <v>519553</v>
       </c>
       <c r="R60" t="n">
-        <v>6524859</v>
+        <v>6524821</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6977,7 +6975,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6987,7 +6985,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -7000,17 +6998,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>på tall</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7029,10 +7023,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985560</v>
+        <v>127985115</v>
       </c>
       <c r="B61" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7040,21 +7034,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7073,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519553</v>
+        <v>519590</v>
       </c>
       <c r="R61" t="n">
-        <v>6524821</v>
+        <v>6524878</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7136,7 +7130,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127985115</v>
+        <v>127980055</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7180,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519590</v>
+        <v>519943</v>
       </c>
       <c r="R62" t="n">
-        <v>6524878</v>
+        <v>6524799</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7195,7 +7189,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7205,7 +7199,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7224,7 +7218,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7243,43 +7236,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980055</v>
+        <v>127980871</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7287,10 +7282,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519943</v>
+        <v>519964</v>
       </c>
       <c r="R63" t="n">
-        <v>6524799</v>
+        <v>6524859</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7323,6 +7318,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7349,10 +7349,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127983362</v>
+        <v>127989334</v>
       </c>
       <c r="B64" t="n">
-        <v>8439</v>
+        <v>96185</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,32 +7360,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7393,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519743</v>
+        <v>519962</v>
       </c>
       <c r="R64" t="n">
-        <v>6524836</v>
+        <v>6524616</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7456,10 +7455,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127989334</v>
+        <v>127983362</v>
       </c>
       <c r="B65" t="n">
-        <v>96173</v>
+        <v>8439</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7467,31 +7466,32 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519962</v>
+        <v>519743</v>
       </c>
       <c r="R65" t="n">
-        <v>6524616</v>
+        <v>6524836</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127948538</v>
+        <v>127986450</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>92782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,27 +799,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520098</v>
+        <v>519639</v>
       </c>
       <c r="R3" t="n">
-        <v>6524835</v>
+        <v>6524788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1001,41 +1002,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986450</v>
+        <v>127986585</v>
       </c>
       <c r="B5" t="n">
-        <v>92782</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519639</v>
+        <v>519663</v>
       </c>
       <c r="R5" t="n">
-        <v>6524788</v>
+        <v>6524783</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127986585</v>
+        <v>127988398</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1150,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519663</v>
+        <v>519897</v>
       </c>
       <c r="R6" t="n">
-        <v>6524783</v>
+        <v>6524632</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127988398</v>
+        <v>127981516</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1257,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519897</v>
+        <v>519856</v>
       </c>
       <c r="R7" t="n">
-        <v>6524632</v>
+        <v>6524816</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127981516</v>
+        <v>127980622</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1364,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519856</v>
+        <v>519968</v>
       </c>
       <c r="R8" t="n">
-        <v>6524816</v>
+        <v>6524851</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1408,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127980622</v>
+        <v>127979097</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>40086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519968</v>
+        <v>520012</v>
       </c>
       <c r="R9" t="n">
-        <v>6524851</v>
+        <v>6524809</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1507,6 +1509,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,43 +1540,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127979097</v>
+        <v>127948538</v>
       </c>
       <c r="B10" t="n">
-        <v>40086</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>214803</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520012</v>
+        <v>520098</v>
       </c>
       <c r="R10" t="n">
-        <v>6524809</v>
+        <v>6524835</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R40" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127986860</v>
+        <v>127988102</v>
       </c>
       <c r="B41" t="n">
         <v>8450</v>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519744</v>
+        <v>519876</v>
       </c>
       <c r="R41" t="n">
-        <v>6524735</v>
+        <v>6524610</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127984457</v>
+        <v>127981257</v>
       </c>
       <c r="B56" t="n">
-        <v>6272</v>
+        <v>79173</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,32 +6502,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105336</v>
+        <v>6450</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6535,10 +6533,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519670</v>
+        <v>519957</v>
       </c>
       <c r="R56" t="n">
-        <v>6524879</v>
+        <v>6524845</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6598,10 +6596,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127979259</v>
+        <v>127984457</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>6272</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6609,32 +6607,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6642,10 +6640,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520006</v>
+        <v>519670</v>
       </c>
       <c r="R57" t="n">
-        <v>6524801</v>
+        <v>6524879</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6686,6 +6684,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6704,7 +6703,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127984642</v>
+        <v>127979259</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6748,10 +6747,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519633</v>
+        <v>520006</v>
       </c>
       <c r="R58" t="n">
-        <v>6524919</v>
+        <v>6524801</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6792,7 +6791,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6811,10 +6809,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127981257</v>
+        <v>127984642</v>
       </c>
       <c r="B59" t="n">
-        <v>79173</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6822,30 +6820,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6450</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519957</v>
+        <v>519633</v>
       </c>
       <c r="R59" t="n">
-        <v>6524845</v>
+        <v>6524919</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6916,43 +6916,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127985560</v>
+        <v>127980871</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6960,10 +6962,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519553</v>
+        <v>519964</v>
       </c>
       <c r="R60" t="n">
-        <v>6524821</v>
+        <v>6524859</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6975,7 +6977,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6985,7 +6987,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -6998,13 +7000,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>på tall</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7023,10 +7029,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985115</v>
+        <v>127985560</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>8439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7034,21 +7040,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7073,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519590</v>
+        <v>519553</v>
       </c>
       <c r="R61" t="n">
-        <v>6524878</v>
+        <v>6524821</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7130,7 +7136,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127980055</v>
+        <v>127985115</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7174,10 +7180,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519943</v>
+        <v>519590</v>
       </c>
       <c r="R62" t="n">
-        <v>6524799</v>
+        <v>6524878</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7189,7 +7195,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7199,7 +7205,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7218,6 +7224,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7236,45 +7243,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980871</v>
+        <v>127980055</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7282,10 +7287,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519964</v>
+        <v>519943</v>
       </c>
       <c r="R63" t="n">
-        <v>6524859</v>
+        <v>6524799</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7318,11 +7323,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127986450</v>
+        <v>127948538</v>
       </c>
       <c r="B3" t="n">
-        <v>92782</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,27 +799,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519639</v>
+        <v>520098</v>
       </c>
       <c r="R3" t="n">
-        <v>6524788</v>
+        <v>6524835</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1002,43 +1001,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986585</v>
+        <v>127986450</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>92782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519663</v>
+        <v>519639</v>
       </c>
       <c r="R5" t="n">
-        <v>6524783</v>
+        <v>6524788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127988398</v>
+        <v>127986585</v>
       </c>
       <c r="B6" t="n">
         <v>8450</v>
@@ -1153,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519897</v>
+        <v>519663</v>
       </c>
       <c r="R6" t="n">
-        <v>6524632</v>
+        <v>6524783</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127981516</v>
+        <v>127988398</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1260,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519856</v>
+        <v>519897</v>
       </c>
       <c r="R7" t="n">
-        <v>6524816</v>
+        <v>6524632</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1323,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127980622</v>
+        <v>127981516</v>
       </c>
       <c r="B8" t="n">
         <v>8450</v>
@@ -1367,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519968</v>
+        <v>519856</v>
       </c>
       <c r="R8" t="n">
-        <v>6524851</v>
+        <v>6524816</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1411,6 +1408,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127979097</v>
+        <v>127980622</v>
       </c>
       <c r="B9" t="n">
-        <v>40086</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520012</v>
+        <v>519968</v>
       </c>
       <c r="R9" t="n">
-        <v>6524809</v>
+        <v>6524851</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1509,11 +1507,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,41 +1533,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127948538</v>
+        <v>127979097</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>40086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>214803</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520098</v>
+        <v>520012</v>
       </c>
       <c r="R10" t="n">
-        <v>6524835</v>
+        <v>6524809</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127986860</v>
+        <v>127988102</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519744</v>
+        <v>519876</v>
       </c>
       <c r="R40" t="n">
-        <v>6524735</v>
+        <v>6524610</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B41" t="n">
         <v>8450</v>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R41" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -6491,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127981257</v>
+        <v>127984457</v>
       </c>
       <c r="B56" t="n">
-        <v>79173</v>
+        <v>6272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,30 +6502,32 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6450</v>
+        <v>105336</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6533,10 +6535,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519957</v>
+        <v>519670</v>
       </c>
       <c r="R56" t="n">
-        <v>6524845</v>
+        <v>6524879</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6596,10 +6598,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127984457</v>
+        <v>127979259</v>
       </c>
       <c r="B57" t="n">
-        <v>6272</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6607,32 +6609,32 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6640,10 +6642,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519670</v>
+        <v>520006</v>
       </c>
       <c r="R57" t="n">
-        <v>6524879</v>
+        <v>6524801</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6684,7 +6686,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6703,7 +6704,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127979259</v>
+        <v>127984642</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6747,10 +6748,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520006</v>
+        <v>519633</v>
       </c>
       <c r="R58" t="n">
-        <v>6524801</v>
+        <v>6524919</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6791,6 +6792,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6809,10 +6811,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127984642</v>
+        <v>127981257</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79173</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6820,32 +6822,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6450</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519633</v>
+        <v>519957</v>
       </c>
       <c r="R59" t="n">
-        <v>6524919</v>
+        <v>6524845</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6916,45 +6916,43 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127980871</v>
+        <v>127985560</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>8439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6962,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519964</v>
+        <v>519553</v>
       </c>
       <c r="R60" t="n">
-        <v>6524859</v>
+        <v>6524821</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6977,7 +6975,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6987,7 +6985,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -7000,17 +6998,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>på tall</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7029,10 +7023,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985560</v>
+        <v>127985115</v>
       </c>
       <c r="B61" t="n">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7040,21 +7034,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7073,10 +7067,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519553</v>
+        <v>519590</v>
       </c>
       <c r="R61" t="n">
-        <v>6524821</v>
+        <v>6524878</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7136,7 +7130,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127985115</v>
+        <v>127980055</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7180,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519590</v>
+        <v>519943</v>
       </c>
       <c r="R62" t="n">
-        <v>6524878</v>
+        <v>6524799</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7195,7 +7189,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7205,7 +7199,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -7224,7 +7218,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7243,43 +7236,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980055</v>
+        <v>127980871</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7287,10 +7282,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519943</v>
+        <v>519964</v>
       </c>
       <c r="R63" t="n">
-        <v>6524799</v>
+        <v>6524859</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7323,6 +7318,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89002267</v>
+        <v>127984700</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hallsberg, Nrk</t>
+          <t>Hjortmon, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519852.5096271439</v>
+        <v>519633</v>
       </c>
       <c r="R2" t="n">
-        <v>6524589.227508585</v>
+        <v>6524919</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,59 +761,61 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127948538</v>
+        <v>127979875</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520098</v>
+        <v>519924</v>
       </c>
       <c r="R3" t="n">
-        <v>6524835</v>
+        <v>6524793</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,46 +885,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127983115</v>
+        <v>127983788</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519891</v>
+        <v>519717</v>
       </c>
       <c r="R4" t="n">
-        <v>6524716</v>
+        <v>6524808</v>
       </c>
       <c r="S4" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,41 +991,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127986450</v>
+        <v>127988256</v>
       </c>
       <c r="B5" t="n">
-        <v>92782</v>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519639</v>
+        <v>519889</v>
       </c>
       <c r="R5" t="n">
-        <v>6524788</v>
+        <v>6524614</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127986585</v>
+        <v>127989334</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,32 +1108,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519663</v>
+        <v>519962</v>
       </c>
       <c r="R6" t="n">
-        <v>6524783</v>
+        <v>6524616</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,43 +1203,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127988398</v>
+        <v>127986395</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519897</v>
+        <v>519639</v>
       </c>
       <c r="R7" t="n">
-        <v>6524632</v>
+        <v>6524788</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,43 +1308,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127981516</v>
+        <v>127978914</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519856</v>
+        <v>520021</v>
       </c>
       <c r="R8" t="n">
-        <v>6524816</v>
+        <v>6524832</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1408,7 +1394,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,54 +1412,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127980622</v>
+        <v>89002267</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hjortmon, Nrk</t>
+          <t>Hallsberg, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519968</v>
+        <v>519853</v>
       </c>
       <c r="R9" t="n">
-        <v>6524851</v>
+        <v>6524589</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1501,12 +1478,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,55 +1498,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127979097</v>
+        <v>127980871</v>
       </c>
       <c r="B10" t="n">
-        <v>40086</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>214803</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1577,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520012</v>
+        <v>519964</v>
       </c>
       <c r="R10" t="n">
-        <v>6524809</v>
+        <v>6524859</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1617,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Kläckhål på björk</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,43 +1623,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127984949</v>
+        <v>127981257</v>
       </c>
       <c r="B11" t="n">
-        <v>40086</v>
+        <v>79413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>214803</v>
+        <v>6450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1688,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519552</v>
+        <v>519957</v>
       </c>
       <c r="R11" t="n">
-        <v>6524907</v>
+        <v>6524845</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1703,7 +1680,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1713,7 +1690,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1724,11 +1701,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,43 +1728,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127981103</v>
+        <v>127948538</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1800,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519953</v>
+        <v>520098</v>
       </c>
       <c r="R12" t="n">
-        <v>6524860</v>
+        <v>6524835</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1862,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127988511</v>
+        <v>127983115</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,30 +1843,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1906,13 +1879,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519885</v>
+        <v>519891</v>
       </c>
       <c r="R13" t="n">
-        <v>6524640</v>
+        <v>6524716</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1950,7 +1923,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127948647</v>
+        <v>127981664</v>
       </c>
       <c r="B14" t="n">
-        <v>40086</v>
+        <v>4775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1952,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>214803</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2013,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520100</v>
+        <v>519843</v>
       </c>
       <c r="R14" t="n">
-        <v>6524842</v>
+        <v>6524831</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2051,17 +2023,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2080,41 +2048,44 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127949128</v>
+        <v>127983089</v>
       </c>
       <c r="B15" t="n">
-        <v>40086</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>214803</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2124,13 +2095,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520070</v>
+        <v>519891</v>
       </c>
       <c r="R15" t="n">
-        <v>6524851</v>
+        <v>6524716</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2160,11 +2131,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127979875</v>
+        <v>127984457</v>
       </c>
       <c r="B16" t="n">
-        <v>96185</v>
+        <v>6274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,31 +2168,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>105336</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2234,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519924</v>
+        <v>519670</v>
       </c>
       <c r="R16" t="n">
-        <v>6524793</v>
+        <v>6524879</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2278,6 +2245,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2296,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127985911</v>
+        <v>127948430</v>
       </c>
       <c r="B17" t="n">
-        <v>40086</v>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519623</v>
+        <v>520103</v>
       </c>
       <c r="R17" t="n">
-        <v>6524788</v>
+        <v>6524835</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2355,7 +2323,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2365,7 +2333,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2378,18 +2346,12 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127978774</v>
+        <v>127948850</v>
       </c>
       <c r="B18" t="n">
-        <v>40086</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,21 +2381,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520015</v>
+        <v>520085</v>
       </c>
       <c r="R18" t="n">
-        <v>6524853</v>
+        <v>6524846</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2488,11 +2450,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,10 +2476,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127985273</v>
+        <v>127949748</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519561</v>
+        <v>520046</v>
       </c>
       <c r="R19" t="n">
-        <v>6524849</v>
+        <v>6524882</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2535,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2588,7 +2545,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2607,7 +2564,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2626,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127982168</v>
+        <v>127950272</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519819</v>
+        <v>520031</v>
       </c>
       <c r="R20" t="n">
-        <v>6524878</v>
+        <v>6524880</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2714,7 +2670,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127982418</v>
+        <v>127950402</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,10 +2732,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519808</v>
+        <v>520020</v>
       </c>
       <c r="R21" t="n">
-        <v>6524877</v>
+        <v>6524923</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2821,7 +2776,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2840,44 +2794,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127983089</v>
+        <v>127979259</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2887,13 +2838,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519891</v>
+        <v>520006</v>
       </c>
       <c r="R22" t="n">
-        <v>6524716</v>
+        <v>6524801</v>
       </c>
       <c r="S22" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2949,10 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127985397</v>
+        <v>127980055</v>
       </c>
       <c r="B23" t="n">
-        <v>40086</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,21 +2911,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519560</v>
+        <v>519943</v>
       </c>
       <c r="R23" t="n">
-        <v>6524839</v>
+        <v>6524799</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3008,7 +2959,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3018,7 +2969,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3031,18 +2982,12 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3061,10 +3006,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127948923</v>
+        <v>127980473</v>
       </c>
       <c r="B24" t="n">
-        <v>40086</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3072,21 +3017,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3105,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520075</v>
+        <v>519985</v>
       </c>
       <c r="R24" t="n">
-        <v>6524840</v>
+        <v>6524831</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3141,11 +3086,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,10 +3112,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127949748</v>
+        <v>127980622</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520046</v>
+        <v>519968</v>
       </c>
       <c r="R25" t="n">
-        <v>6524882</v>
+        <v>6524851</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3278,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127982588</v>
+        <v>127981103</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,10 +3262,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519798</v>
+        <v>519953</v>
       </c>
       <c r="R26" t="n">
-        <v>6524851</v>
+        <v>6524860</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3366,7 +3306,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3385,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127950272</v>
+        <v>127981516</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3429,10 +3368,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520031</v>
+        <v>519856</v>
       </c>
       <c r="R27" t="n">
-        <v>6524880</v>
+        <v>6524816</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3473,6 +3412,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3491,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127950402</v>
+        <v>127982168</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520020</v>
+        <v>519819</v>
       </c>
       <c r="R28" t="n">
-        <v>6524923</v>
+        <v>6524878</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3579,6 +3519,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3597,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127988256</v>
+        <v>127982266</v>
       </c>
       <c r="B29" t="n">
-        <v>96185</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3608,31 +3549,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3640,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519889</v>
+        <v>519814</v>
       </c>
       <c r="R29" t="n">
-        <v>6524614</v>
+        <v>6524877</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3703,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127984194</v>
+        <v>127982418</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3747,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519680</v>
+        <v>519808</v>
       </c>
       <c r="R30" t="n">
-        <v>6524874</v>
+        <v>6524877</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3810,10 +3752,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127948850</v>
+        <v>127982588</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3854,10 +3796,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520085</v>
+        <v>519798</v>
       </c>
       <c r="R31" t="n">
-        <v>6524846</v>
+        <v>6524851</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3898,6 +3840,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3916,10 +3859,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127984020</v>
+        <v>127983540</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519675</v>
+        <v>519733</v>
       </c>
       <c r="R32" t="n">
-        <v>6524829</v>
+        <v>6524792</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4023,10 +3966,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127948726</v>
+        <v>127984020</v>
       </c>
       <c r="B33" t="n">
-        <v>8439</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,21 +3977,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4067,10 +4010,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520092</v>
+        <v>519675</v>
       </c>
       <c r="R33" t="n">
-        <v>6524842</v>
+        <v>6524829</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4111,6 +4054,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4129,10 +4073,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127948430</v>
+        <v>127984194</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,10 +4117,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520103</v>
+        <v>519680</v>
       </c>
       <c r="R34" t="n">
-        <v>6524835</v>
+        <v>6524874</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4217,6 +4161,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4235,10 +4180,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127987178</v>
+        <v>127984642</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4279,10 +4224,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519677</v>
+        <v>519633</v>
       </c>
       <c r="R35" t="n">
-        <v>6524696</v>
+        <v>6524919</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4342,10 +4287,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127950052</v>
+        <v>127985115</v>
       </c>
       <c r="B36" t="n">
-        <v>40086</v>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,21 +4298,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520044</v>
+        <v>519590</v>
       </c>
       <c r="R36" t="n">
-        <v>6524903</v>
+        <v>6524878</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4401,7 +4346,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4411,7 +4356,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4424,17 +4369,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,41 +4394,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127986395</v>
+        <v>127985273</v>
       </c>
       <c r="B37" t="n">
-        <v>92746</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4495,10 +4438,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519639</v>
+        <v>519561</v>
       </c>
       <c r="R37" t="n">
-        <v>6524788</v>
+        <v>6524849</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4510,7 +4453,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4520,7 +4463,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4558,10 +4501,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127987059</v>
+        <v>127985707</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4602,10 +4545,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519688</v>
+        <v>519596</v>
       </c>
       <c r="R38" t="n">
-        <v>6524694</v>
+        <v>6524811</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4617,7 +4560,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4627,7 +4570,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4665,10 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127978914</v>
+        <v>127986585</v>
       </c>
       <c r="B39" t="n">
-        <v>92754</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4676,30 +4619,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4707,10 +4652,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520021</v>
+        <v>519663</v>
       </c>
       <c r="R39" t="n">
-        <v>6524832</v>
+        <v>6524783</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4751,6 +4696,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4769,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127988102</v>
+        <v>127986860</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4813,10 +4759,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519876</v>
+        <v>519744</v>
       </c>
       <c r="R40" t="n">
-        <v>6524610</v>
+        <v>6524735</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4876,10 +4822,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127986860</v>
+        <v>127987059</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4920,10 +4866,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519744</v>
+        <v>519688</v>
       </c>
       <c r="R41" t="n">
-        <v>6524735</v>
+        <v>6524694</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4983,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127982266</v>
+        <v>127987178</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,10 +4973,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519814</v>
+        <v>519677</v>
       </c>
       <c r="R42" t="n">
-        <v>6524877</v>
+        <v>6524696</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5090,10 +5036,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127980473</v>
+        <v>127987309</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5134,10 +5080,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519985</v>
+        <v>519658</v>
       </c>
       <c r="R43" t="n">
-        <v>6524831</v>
+        <v>6524711</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5178,6 +5124,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5196,10 +5143,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127983788</v>
+        <v>127987902</v>
       </c>
       <c r="B44" t="n">
-        <v>96185</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,31 +5154,32 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5239,10 +5187,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519717</v>
+        <v>519738</v>
       </c>
       <c r="R44" t="n">
-        <v>6524808</v>
+        <v>6524605</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5302,10 +5250,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127981664</v>
+        <v>127988102</v>
       </c>
       <c r="B45" t="n">
-        <v>4773</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5313,21 +5261,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5294,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519843</v>
+        <v>519876</v>
       </c>
       <c r="R45" t="n">
-        <v>6524831</v>
+        <v>6524610</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5409,10 +5357,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127979704</v>
+        <v>127988398</v>
       </c>
       <c r="B46" t="n">
-        <v>40086</v>
+        <v>8455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5420,21 +5368,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>214803</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5453,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519952</v>
+        <v>519897</v>
       </c>
       <c r="R46" t="n">
-        <v>6524773</v>
+        <v>6524632</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5491,17 +5439,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5520,41 +5464,43 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127984700</v>
+        <v>127988511</v>
       </c>
       <c r="B47" t="n">
-        <v>81072</v>
+        <v>8455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5562,10 +5508,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519633</v>
+        <v>519885</v>
       </c>
       <c r="R47" t="n">
-        <v>6524919</v>
+        <v>6524640</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5625,10 +5571,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127985707</v>
+        <v>127948726</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>8444</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5636,21 +5582,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5669,10 +5615,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519596</v>
+        <v>520092</v>
       </c>
       <c r="R48" t="n">
-        <v>6524811</v>
+        <v>6524842</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5684,7 +5630,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5694,7 +5640,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5713,7 +5659,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5732,10 +5677,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127980279</v>
+        <v>127950593</v>
       </c>
       <c r="B49" t="n">
-        <v>40086</v>
+        <v>8444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5743,21 +5688,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5776,10 +5721,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519975</v>
+        <v>519991</v>
       </c>
       <c r="R49" t="n">
-        <v>6524804</v>
+        <v>6524893</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5812,11 +5757,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5843,10 +5783,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127949357</v>
+        <v>127979471</v>
       </c>
       <c r="B50" t="n">
-        <v>40086</v>
+        <v>8444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5854,21 +5794,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5827,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520055</v>
+        <v>519986</v>
       </c>
       <c r="R50" t="n">
-        <v>6524858</v>
+        <v>6524777</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5923,11 +5863,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5954,10 +5889,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127949218</v>
+        <v>127983362</v>
       </c>
       <c r="B51" t="n">
-        <v>40086</v>
+        <v>8444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5965,21 +5900,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>214803</v>
+        <v>106554</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5998,10 +5933,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520067</v>
+        <v>519743</v>
       </c>
       <c r="R51" t="n">
-        <v>6524857</v>
+        <v>6524836</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6036,17 +5971,13 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6065,10 +5996,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127950593</v>
+        <v>127985560</v>
       </c>
       <c r="B52" t="n">
-        <v>8439</v>
+        <v>8444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6109,10 +6040,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519991</v>
+        <v>519553</v>
       </c>
       <c r="R52" t="n">
-        <v>6524893</v>
+        <v>6524821</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6124,7 +6055,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6134,7 +6065,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -6153,6 +6084,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6103,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127979471</v>
+        <v>127948354</v>
       </c>
       <c r="B53" t="n">
-        <v>8439</v>
+        <v>40300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,21 +6114,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6215,10 +6147,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519986</v>
+        <v>520111</v>
       </c>
       <c r="R53" t="n">
-        <v>6524777</v>
+        <v>6524833</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6251,6 +6183,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,10 +6214,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127987902</v>
+        <v>127948647</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>40300</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6288,21 +6225,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6321,10 +6258,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519738</v>
+        <v>520100</v>
       </c>
       <c r="R54" t="n">
-        <v>6524605</v>
+        <v>6524842</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6359,13 +6296,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6384,10 +6325,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127983540</v>
+        <v>127948923</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>40300</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6395,21 +6336,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6428,10 +6369,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519733</v>
+        <v>520075</v>
       </c>
       <c r="R55" t="n">
-        <v>6524792</v>
+        <v>6524840</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6466,13 +6407,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6491,10 +6436,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127984457</v>
+        <v>127949128</v>
       </c>
       <c r="B56" t="n">
-        <v>6272</v>
+        <v>40300</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,32 +6447,32 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105336</v>
+        <v>214803</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6535,10 +6480,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519670</v>
+        <v>520070</v>
       </c>
       <c r="R56" t="n">
-        <v>6524879</v>
+        <v>6524851</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6573,13 +6518,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6598,10 +6547,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127979259</v>
+        <v>127949218</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>40300</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6609,21 +6558,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6642,10 +6591,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520006</v>
+        <v>520067</v>
       </c>
       <c r="R57" t="n">
-        <v>6524801</v>
+        <v>6524857</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6678,6 +6627,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6704,10 +6658,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127984642</v>
+        <v>127949357</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>40300</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6715,21 +6669,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6748,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519633</v>
+        <v>520055</v>
       </c>
       <c r="R58" t="n">
-        <v>6524919</v>
+        <v>6524858</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6786,13 +6740,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6811,10 +6769,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127981257</v>
+        <v>127950052</v>
       </c>
       <c r="B59" t="n">
-        <v>79173</v>
+        <v>40300</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6822,30 +6780,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6450</v>
+        <v>214803</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6853,10 +6813,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519957</v>
+        <v>520044</v>
       </c>
       <c r="R59" t="n">
-        <v>6524845</v>
+        <v>6524903</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6891,13 +6851,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6916,10 +6880,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127985560</v>
+        <v>127978774</v>
       </c>
       <c r="B60" t="n">
-        <v>8439</v>
+        <v>40300</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6927,21 +6891,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6960,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519553</v>
+        <v>520015</v>
       </c>
       <c r="R60" t="n">
-        <v>6524821</v>
+        <v>6524853</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6975,7 +6939,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6985,7 +6949,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -6998,13 +6962,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7023,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127985115</v>
+        <v>127979097</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>40300</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7034,21 +7002,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,10 +7035,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519590</v>
+        <v>520012</v>
       </c>
       <c r="R61" t="n">
-        <v>6524878</v>
+        <v>6524809</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7082,7 +7050,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -7092,7 +7060,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Lerbäck</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -7105,13 +7073,17 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7130,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127980055</v>
+        <v>127979704</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>40300</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7141,21 +7113,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7174,10 +7146,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519943</v>
+        <v>519952</v>
       </c>
       <c r="R62" t="n">
-        <v>6524799</v>
+        <v>6524773</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7210,6 +7182,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7236,45 +7213,43 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127980871</v>
+        <v>127980279</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>40300</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>214803</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7282,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519964</v>
+        <v>519975</v>
       </c>
       <c r="R63" t="n">
-        <v>6524859</v>
+        <v>6524804</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7322,7 +7297,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7349,10 +7324,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127989334</v>
+        <v>127984949</v>
       </c>
       <c r="B64" t="n">
-        <v>96185</v>
+        <v>40300</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7360,31 +7335,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2180</v>
+        <v>214803</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7392,10 +7368,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519962</v>
+        <v>519552</v>
       </c>
       <c r="R64" t="n">
-        <v>6524616</v>
+        <v>6524907</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7407,7 +7383,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7417,7 +7393,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -7428,6 +7404,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7455,10 +7436,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127983362</v>
+        <v>127985397</v>
       </c>
       <c r="B65" t="n">
-        <v>8439</v>
+        <v>40300</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7466,21 +7447,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>214803</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7499,10 +7480,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519743</v>
+        <v>519560</v>
       </c>
       <c r="R65" t="n">
-        <v>6524836</v>
+        <v>6524839</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7514,7 +7495,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7524,7 +7505,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Lerbäck</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -7535,6 +7516,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7559,6 +7545,223 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127985911</v>
+      </c>
+      <c r="B66" t="n">
+        <v>40300</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>519623</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6524788</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127983590</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>519733</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6524792</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37787-2025 artfynd.xlsx
+++ b/artfynd/A 37787-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127984700</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127979875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127983788</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127988256</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127989334</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127986395</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127978914</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89002267</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127980871</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127981257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127948538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127983115</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127981664</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2154,6 +2224,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127983089</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127984457</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2367,6 +2447,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127948430</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2473,6 +2558,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127948850</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2579,6 +2669,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127949748</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127950272</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2791,6 +2891,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127950402</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2897,6 +3002,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127979259</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3003,6 +3113,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127980055</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127980473</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3215,6 +3335,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127980622</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3321,6 +3446,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127981103</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3428,6 +3558,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127981516</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3535,6 +3670,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127982168</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3642,6 +3782,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127982266</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3749,6 +3894,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127982418</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3856,6 +4006,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127982588</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3963,6 +4118,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127983540</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4070,6 +4230,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127984020</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4177,6 +4342,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127984194</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4284,6 +4454,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127984642</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4391,6 +4566,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127985115</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4498,6 +4678,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127985273</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4605,6 +4790,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127985707</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4712,6 +4902,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127986585</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4819,6 +5014,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127986860</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4926,6 +5126,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127987059</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5033,6 +5238,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127987178</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5140,6 +5350,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127987309</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5247,6 +5462,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127987902</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5354,6 +5574,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127988102</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5461,6 +5686,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127988398</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5568,6 +5798,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127988511</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5674,6 +5909,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127948726</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5780,6 +6020,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127950593</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5886,6 +6131,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127979471</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5993,6 +6243,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127983362</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6100,6 +6355,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127985560</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6211,6 +6471,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127948354</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6322,6 +6587,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127948647</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6433,6 +6703,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127948923</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6544,6 +6819,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127949128</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6655,6 +6935,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127949218</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6766,6 +7051,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127949357</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6877,6 +7167,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127950052</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6988,6 +7283,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127978774</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7099,6 +7399,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127979097</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7210,6 +7515,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127979704</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7321,6 +7631,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127980279</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7433,6 +7748,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127984949</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7545,6 +7865,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127985397</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7657,6 +7982,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127985911</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7762,8 +8092,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127983590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>